--- a/doc/PGT测试清单模板.xlsx
+++ b/doc/PGT测试清单模板.xlsx
@@ -11,7 +11,9 @@
     <sheet name="按模块汇总" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="映射说明" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'功能测试清单'!$A$1:$J$675</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,16 +32,30 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -47,15 +63,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -424,8 +462,20 @@
   </sheetPr>
   <dimension ref="A1:J675"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>序号</t>
@@ -477,7 +527,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -511,7 +561,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="28" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -545,7 +595,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -579,7 +629,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="28" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -613,7 +663,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="28" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -647,7 +697,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="28" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -681,7 +731,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="28" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -715,7 +765,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="28" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
@@ -749,7 +799,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="28" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
@@ -783,7 +833,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="28" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
@@ -817,7 +867,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="28" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
@@ -851,7 +901,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="28" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -885,7 +935,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="28" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -919,7 +969,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="28" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
@@ -953,7 +1003,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="28" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -987,7 +1037,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="28" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -1021,7 +1071,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="28" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
@@ -1055,7 +1105,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="28" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
@@ -1089,7 +1139,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="28" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
@@ -1123,7 +1173,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="28" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
@@ -1157,7 +1207,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="28" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
@@ -1191,7 +1241,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="28" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
@@ -1225,7 +1275,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="28" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
@@ -1259,7 +1309,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="28" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
@@ -1293,7 +1343,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="28" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
@@ -1327,7 +1377,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="28" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
@@ -1361,7 +1411,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="28" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
@@ -1395,7 +1445,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="28" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
@@ -1429,7 +1479,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="28" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
@@ -1463,7 +1513,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="28" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
@@ -1497,7 +1547,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="28" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
@@ -1531,7 +1581,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="28" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
@@ -1565,7 +1615,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="28" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
@@ -1599,7 +1649,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="28" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
@@ -1633,7 +1683,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="28" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
@@ -1667,7 +1717,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="28" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
@@ -1701,7 +1751,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="28" customHeight="1">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
@@ -1735,7 +1785,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="28" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
@@ -1769,7 +1819,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="28" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
@@ -1803,7 +1853,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="28" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
@@ -1837,7 +1887,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="28" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
@@ -1871,7 +1921,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="28" customHeight="1">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
@@ -1905,7 +1955,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="28" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
@@ -1939,7 +1989,7 @@
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="28" customHeight="1">
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
@@ -1973,7 +2023,7 @@
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="28" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
@@ -2007,7 +2057,7 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="28" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
@@ -2041,7 +2091,7 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="28" customHeight="1">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
@@ -2075,7 +2125,7 @@
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="28" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
@@ -2109,7 +2159,7 @@
         </is>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="28" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
@@ -2143,7 +2193,7 @@
         </is>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="28" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
@@ -2177,7 +2227,7 @@
         </is>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="28" customHeight="1">
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
@@ -2211,7 +2261,7 @@
         </is>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="28" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
@@ -2245,7 +2295,7 @@
         </is>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="28" customHeight="1">
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
@@ -2279,7 +2329,7 @@
         </is>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="28" customHeight="1">
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
@@ -2313,7 +2363,7 @@
         </is>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="28" customHeight="1">
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
@@ -2347,7 +2397,7 @@
         </is>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="28" customHeight="1">
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
@@ -2381,7 +2431,7 @@
         </is>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="28" customHeight="1">
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
@@ -2415,7 +2465,7 @@
         </is>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="28" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
@@ -2449,7 +2499,7 @@
         </is>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="28" customHeight="1">
       <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
@@ -2483,7 +2533,7 @@
         </is>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="28" customHeight="1">
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
@@ -2517,7 +2567,7 @@
         </is>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="28" customHeight="1">
       <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
@@ -2551,7 +2601,7 @@
         </is>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="28" customHeight="1">
       <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
@@ -2585,7 +2635,7 @@
         </is>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="28" customHeight="1">
       <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
@@ -2619,7 +2669,7 @@
         </is>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="28" customHeight="1">
       <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
@@ -2653,7 +2703,7 @@
         </is>
       </c>
     </row>
-    <row r="66">
+    <row r="66" ht="28" customHeight="1">
       <c r="A66" s="2" t="n">
         <v>65</v>
       </c>
@@ -2687,7 +2737,7 @@
         </is>
       </c>
     </row>
-    <row r="67">
+    <row r="67" ht="28" customHeight="1">
       <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
@@ -2721,7 +2771,7 @@
         </is>
       </c>
     </row>
-    <row r="68">
+    <row r="68" ht="28" customHeight="1">
       <c r="A68" s="2" t="n">
         <v>67</v>
       </c>
@@ -2755,7 +2805,7 @@
         </is>
       </c>
     </row>
-    <row r="69">
+    <row r="69" ht="28" customHeight="1">
       <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
@@ -2789,7 +2839,7 @@
         </is>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="28" customHeight="1">
       <c r="A70" s="2" t="n">
         <v>69</v>
       </c>
@@ -2823,7 +2873,7 @@
         </is>
       </c>
     </row>
-    <row r="71">
+    <row r="71" ht="28" customHeight="1">
       <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
@@ -2857,7 +2907,7 @@
         </is>
       </c>
     </row>
-    <row r="72">
+    <row r="72" ht="28" customHeight="1">
       <c r="A72" s="2" t="n">
         <v>71</v>
       </c>
@@ -2891,7 +2941,7 @@
         </is>
       </c>
     </row>
-    <row r="73">
+    <row r="73" ht="28" customHeight="1">
       <c r="A73" s="2" t="n">
         <v>72</v>
       </c>
@@ -2925,7 +2975,7 @@
         </is>
       </c>
     </row>
-    <row r="74">
+    <row r="74" ht="28" customHeight="1">
       <c r="A74" s="2" t="n">
         <v>73</v>
       </c>
@@ -2959,7 +3009,7 @@
         </is>
       </c>
     </row>
-    <row r="75">
+    <row r="75" ht="28" customHeight="1">
       <c r="A75" s="2" t="n">
         <v>74</v>
       </c>
@@ -2993,7 +3043,7 @@
         </is>
       </c>
     </row>
-    <row r="76">
+    <row r="76" ht="28" customHeight="1">
       <c r="A76" s="2" t="n">
         <v>75</v>
       </c>
@@ -3027,7 +3077,7 @@
         </is>
       </c>
     </row>
-    <row r="77">
+    <row r="77" ht="28" customHeight="1">
       <c r="A77" s="2" t="n">
         <v>76</v>
       </c>
@@ -3061,7 +3111,7 @@
         </is>
       </c>
     </row>
-    <row r="78">
+    <row r="78" ht="28" customHeight="1">
       <c r="A78" s="2" t="n">
         <v>77</v>
       </c>
@@ -3095,7 +3145,7 @@
         </is>
       </c>
     </row>
-    <row r="79">
+    <row r="79" ht="28" customHeight="1">
       <c r="A79" s="2" t="n">
         <v>78</v>
       </c>
@@ -3129,7 +3179,7 @@
         </is>
       </c>
     </row>
-    <row r="80">
+    <row r="80" ht="28" customHeight="1">
       <c r="A80" s="2" t="n">
         <v>79</v>
       </c>
@@ -3163,7 +3213,7 @@
         </is>
       </c>
     </row>
-    <row r="81">
+    <row r="81" ht="28" customHeight="1">
       <c r="A81" s="2" t="n">
         <v>80</v>
       </c>
@@ -3197,7 +3247,7 @@
         </is>
       </c>
     </row>
-    <row r="82">
+    <row r="82" ht="28" customHeight="1">
       <c r="A82" s="2" t="n">
         <v>81</v>
       </c>
@@ -3231,7 +3281,7 @@
         </is>
       </c>
     </row>
-    <row r="83">
+    <row r="83" ht="28" customHeight="1">
       <c r="A83" s="2" t="n">
         <v>82</v>
       </c>
@@ -3265,7 +3315,7 @@
         </is>
       </c>
     </row>
-    <row r="84">
+    <row r="84" ht="28" customHeight="1">
       <c r="A84" s="2" t="n">
         <v>83</v>
       </c>
@@ -3299,7 +3349,7 @@
         </is>
       </c>
     </row>
-    <row r="85">
+    <row r="85" ht="28" customHeight="1">
       <c r="A85" s="2" t="n">
         <v>84</v>
       </c>
@@ -3333,7 +3383,7 @@
         </is>
       </c>
     </row>
-    <row r="86">
+    <row r="86" ht="28" customHeight="1">
       <c r="A86" s="2" t="n">
         <v>85</v>
       </c>
@@ -3367,7 +3417,7 @@
         </is>
       </c>
     </row>
-    <row r="87">
+    <row r="87" ht="28" customHeight="1">
       <c r="A87" s="2" t="n">
         <v>86</v>
       </c>
@@ -3401,7 +3451,7 @@
         </is>
       </c>
     </row>
-    <row r="88">
+    <row r="88" ht="28" customHeight="1">
       <c r="A88" s="2" t="n">
         <v>87</v>
       </c>
@@ -3435,7 +3485,7 @@
         </is>
       </c>
     </row>
-    <row r="89">
+    <row r="89" ht="28" customHeight="1">
       <c r="A89" s="2" t="n">
         <v>88</v>
       </c>
@@ -3469,7 +3519,7 @@
         </is>
       </c>
     </row>
-    <row r="90">
+    <row r="90" ht="28" customHeight="1">
       <c r="A90" s="2" t="n">
         <v>89</v>
       </c>
@@ -3503,7 +3553,7 @@
         </is>
       </c>
     </row>
-    <row r="91">
+    <row r="91" ht="28" customHeight="1">
       <c r="A91" s="2" t="n">
         <v>90</v>
       </c>
@@ -3537,7 +3587,7 @@
         </is>
       </c>
     </row>
-    <row r="92">
+    <row r="92" ht="28" customHeight="1">
       <c r="A92" s="2" t="n">
         <v>91</v>
       </c>
@@ -3571,7 +3621,7 @@
         </is>
       </c>
     </row>
-    <row r="93">
+    <row r="93" ht="28" customHeight="1">
       <c r="A93" s="2" t="n">
         <v>92</v>
       </c>
@@ -3605,7 +3655,7 @@
         </is>
       </c>
     </row>
-    <row r="94">
+    <row r="94" ht="28" customHeight="1">
       <c r="A94" s="2" t="n">
         <v>93</v>
       </c>
@@ -3639,7 +3689,7 @@
         </is>
       </c>
     </row>
-    <row r="95">
+    <row r="95" ht="28" customHeight="1">
       <c r="A95" s="2" t="n">
         <v>94</v>
       </c>
@@ -3673,7 +3723,7 @@
         </is>
       </c>
     </row>
-    <row r="96">
+    <row r="96" ht="28" customHeight="1">
       <c r="A96" s="2" t="n">
         <v>95</v>
       </c>
@@ -3707,7 +3757,7 @@
         </is>
       </c>
     </row>
-    <row r="97">
+    <row r="97" ht="28" customHeight="1">
       <c r="A97" s="2" t="n">
         <v>96</v>
       </c>
@@ -3741,7 +3791,7 @@
         </is>
       </c>
     </row>
-    <row r="98">
+    <row r="98" ht="28" customHeight="1">
       <c r="A98" s="2" t="n">
         <v>97</v>
       </c>
@@ -3775,7 +3825,7 @@
         </is>
       </c>
     </row>
-    <row r="99">
+    <row r="99" ht="28" customHeight="1">
       <c r="A99" s="2" t="n">
         <v>98</v>
       </c>
@@ -3809,7 +3859,7 @@
         </is>
       </c>
     </row>
-    <row r="100">
+    <row r="100" ht="28" customHeight="1">
       <c r="A100" s="2" t="n">
         <v>99</v>
       </c>
@@ -3843,7 +3893,7 @@
         </is>
       </c>
     </row>
-    <row r="101">
+    <row r="101" ht="28" customHeight="1">
       <c r="A101" s="2" t="n">
         <v>100</v>
       </c>
@@ -3877,7 +3927,7 @@
         </is>
       </c>
     </row>
-    <row r="102">
+    <row r="102" ht="28" customHeight="1">
       <c r="A102" s="2" t="n">
         <v>101</v>
       </c>
@@ -3911,7 +3961,7 @@
         </is>
       </c>
     </row>
-    <row r="103">
+    <row r="103" ht="28" customHeight="1">
       <c r="A103" s="2" t="n">
         <v>102</v>
       </c>
@@ -3945,7 +3995,7 @@
         </is>
       </c>
     </row>
-    <row r="104">
+    <row r="104" ht="28" customHeight="1">
       <c r="A104" s="2" t="n">
         <v>103</v>
       </c>
@@ -3979,7 +4029,7 @@
         </is>
       </c>
     </row>
-    <row r="105">
+    <row r="105" ht="28" customHeight="1">
       <c r="A105" s="2" t="n">
         <v>104</v>
       </c>
@@ -4013,7 +4063,7 @@
         </is>
       </c>
     </row>
-    <row r="106">
+    <row r="106" ht="28" customHeight="1">
       <c r="A106" s="2" t="n">
         <v>105</v>
       </c>
@@ -4047,7 +4097,7 @@
         </is>
       </c>
     </row>
-    <row r="107">
+    <row r="107" ht="28" customHeight="1">
       <c r="A107" s="2" t="n">
         <v>106</v>
       </c>
@@ -4081,7 +4131,7 @@
         </is>
       </c>
     </row>
-    <row r="108">
+    <row r="108" ht="28" customHeight="1">
       <c r="A108" s="2" t="n">
         <v>107</v>
       </c>
@@ -4115,7 +4165,7 @@
         </is>
       </c>
     </row>
-    <row r="109">
+    <row r="109" ht="28" customHeight="1">
       <c r="A109" s="2" t="n">
         <v>108</v>
       </c>
@@ -4149,7 +4199,7 @@
         </is>
       </c>
     </row>
-    <row r="110">
+    <row r="110" ht="28" customHeight="1">
       <c r="A110" s="2" t="n">
         <v>109</v>
       </c>
@@ -4183,7 +4233,7 @@
         </is>
       </c>
     </row>
-    <row r="111">
+    <row r="111" ht="28" customHeight="1">
       <c r="A111" s="2" t="n">
         <v>110</v>
       </c>
@@ -4217,7 +4267,7 @@
         </is>
       </c>
     </row>
-    <row r="112">
+    <row r="112" ht="28" customHeight="1">
       <c r="A112" s="2" t="n">
         <v>111</v>
       </c>
@@ -4251,7 +4301,7 @@
         </is>
       </c>
     </row>
-    <row r="113">
+    <row r="113" ht="28" customHeight="1">
       <c r="A113" s="2" t="n">
         <v>112</v>
       </c>
@@ -4285,7 +4335,7 @@
         </is>
       </c>
     </row>
-    <row r="114">
+    <row r="114" ht="28" customHeight="1">
       <c r="A114" s="2" t="n">
         <v>113</v>
       </c>
@@ -4319,7 +4369,7 @@
         </is>
       </c>
     </row>
-    <row r="115">
+    <row r="115" ht="28" customHeight="1">
       <c r="A115" s="2" t="n">
         <v>114</v>
       </c>
@@ -4353,7 +4403,7 @@
         </is>
       </c>
     </row>
-    <row r="116">
+    <row r="116" ht="28" customHeight="1">
       <c r="A116" s="2" t="n">
         <v>115</v>
       </c>
@@ -4387,7 +4437,7 @@
         </is>
       </c>
     </row>
-    <row r="117">
+    <row r="117" ht="28" customHeight="1">
       <c r="A117" s="2" t="n">
         <v>116</v>
       </c>
@@ -4421,7 +4471,7 @@
         </is>
       </c>
     </row>
-    <row r="118">
+    <row r="118" ht="28" customHeight="1">
       <c r="A118" s="2" t="n">
         <v>117</v>
       </c>
@@ -4455,7 +4505,7 @@
         </is>
       </c>
     </row>
-    <row r="119">
+    <row r="119" ht="28" customHeight="1">
       <c r="A119" s="2" t="n">
         <v>118</v>
       </c>
@@ -4489,7 +4539,7 @@
         </is>
       </c>
     </row>
-    <row r="120">
+    <row r="120" ht="28" customHeight="1">
       <c r="A120" s="2" t="n">
         <v>119</v>
       </c>
@@ -4523,7 +4573,7 @@
         </is>
       </c>
     </row>
-    <row r="121">
+    <row r="121" ht="28" customHeight="1">
       <c r="A121" s="2" t="n">
         <v>120</v>
       </c>
@@ -4557,7 +4607,7 @@
         </is>
       </c>
     </row>
-    <row r="122">
+    <row r="122" ht="28" customHeight="1">
       <c r="A122" s="2" t="n">
         <v>121</v>
       </c>
@@ -4591,7 +4641,7 @@
         </is>
       </c>
     </row>
-    <row r="123">
+    <row r="123" ht="28" customHeight="1">
       <c r="A123" s="2" t="n">
         <v>122</v>
       </c>
@@ -4625,7 +4675,7 @@
         </is>
       </c>
     </row>
-    <row r="124">
+    <row r="124" ht="28" customHeight="1">
       <c r="A124" s="2" t="n">
         <v>123</v>
       </c>
@@ -4659,7 +4709,7 @@
         </is>
       </c>
     </row>
-    <row r="125">
+    <row r="125" ht="28" customHeight="1">
       <c r="A125" s="2" t="n">
         <v>124</v>
       </c>
@@ -4693,7 +4743,7 @@
         </is>
       </c>
     </row>
-    <row r="126">
+    <row r="126" ht="28" customHeight="1">
       <c r="A126" s="2" t="n">
         <v>125</v>
       </c>
@@ -4727,7 +4777,7 @@
         </is>
       </c>
     </row>
-    <row r="127">
+    <row r="127" ht="28" customHeight="1">
       <c r="A127" s="2" t="n">
         <v>126</v>
       </c>
@@ -4761,7 +4811,7 @@
         </is>
       </c>
     </row>
-    <row r="128">
+    <row r="128" ht="28" customHeight="1">
       <c r="A128" s="2" t="n">
         <v>127</v>
       </c>
@@ -4795,7 +4845,7 @@
         </is>
       </c>
     </row>
-    <row r="129">
+    <row r="129" ht="28" customHeight="1">
       <c r="A129" s="2" t="n">
         <v>128</v>
       </c>
@@ -4829,7 +4879,7 @@
         </is>
       </c>
     </row>
-    <row r="130">
+    <row r="130" ht="28" customHeight="1">
       <c r="A130" s="2" t="n">
         <v>129</v>
       </c>
@@ -4863,7 +4913,7 @@
         </is>
       </c>
     </row>
-    <row r="131">
+    <row r="131" ht="28" customHeight="1">
       <c r="A131" s="2" t="n">
         <v>130</v>
       </c>
@@ -4897,7 +4947,7 @@
         </is>
       </c>
     </row>
-    <row r="132">
+    <row r="132" ht="28" customHeight="1">
       <c r="A132" s="2" t="n">
         <v>131</v>
       </c>
@@ -4931,7 +4981,7 @@
         </is>
       </c>
     </row>
-    <row r="133">
+    <row r="133" ht="28" customHeight="1">
       <c r="A133" s="2" t="n">
         <v>132</v>
       </c>
@@ -4965,7 +5015,7 @@
         </is>
       </c>
     </row>
-    <row r="134">
+    <row r="134" ht="28" customHeight="1">
       <c r="A134" s="2" t="n">
         <v>133</v>
       </c>
@@ -4999,7 +5049,7 @@
         </is>
       </c>
     </row>
-    <row r="135">
+    <row r="135" ht="28" customHeight="1">
       <c r="A135" s="2" t="n">
         <v>134</v>
       </c>
@@ -5033,7 +5083,7 @@
         </is>
       </c>
     </row>
-    <row r="136">
+    <row r="136" ht="28" customHeight="1">
       <c r="A136" s="2" t="n">
         <v>135</v>
       </c>
@@ -5067,7 +5117,7 @@
         </is>
       </c>
     </row>
-    <row r="137">
+    <row r="137" ht="28" customHeight="1">
       <c r="A137" s="2" t="n">
         <v>136</v>
       </c>
@@ -5101,7 +5151,7 @@
         </is>
       </c>
     </row>
-    <row r="138">
+    <row r="138" ht="28" customHeight="1">
       <c r="A138" s="2" t="n">
         <v>137</v>
       </c>
@@ -5135,7 +5185,7 @@
         </is>
       </c>
     </row>
-    <row r="139">
+    <row r="139" ht="28" customHeight="1">
       <c r="A139" s="2" t="n">
         <v>138</v>
       </c>
@@ -5169,7 +5219,7 @@
         </is>
       </c>
     </row>
-    <row r="140">
+    <row r="140" ht="28" customHeight="1">
       <c r="A140" s="2" t="n">
         <v>139</v>
       </c>
@@ -5203,7 +5253,7 @@
         </is>
       </c>
     </row>
-    <row r="141">
+    <row r="141" ht="28" customHeight="1">
       <c r="A141" s="2" t="n">
         <v>140</v>
       </c>
@@ -5237,7 +5287,7 @@
         </is>
       </c>
     </row>
-    <row r="142">
+    <row r="142" ht="28" customHeight="1">
       <c r="A142" s="2" t="n">
         <v>141</v>
       </c>
@@ -5271,7 +5321,7 @@
         </is>
       </c>
     </row>
-    <row r="143">
+    <row r="143" ht="28" customHeight="1">
       <c r="A143" s="2" t="n">
         <v>142</v>
       </c>
@@ -5305,7 +5355,7 @@
         </is>
       </c>
     </row>
-    <row r="144">
+    <row r="144" ht="28" customHeight="1">
       <c r="A144" s="2" t="n">
         <v>143</v>
       </c>
@@ -5339,7 +5389,7 @@
         </is>
       </c>
     </row>
-    <row r="145">
+    <row r="145" ht="28" customHeight="1">
       <c r="A145" s="2" t="n">
         <v>144</v>
       </c>
@@ -5373,7 +5423,7 @@
         </is>
       </c>
     </row>
-    <row r="146">
+    <row r="146" ht="28" customHeight="1">
       <c r="A146" s="2" t="n">
         <v>145</v>
       </c>
@@ -5407,7 +5457,7 @@
         </is>
       </c>
     </row>
-    <row r="147">
+    <row r="147" ht="28" customHeight="1">
       <c r="A147" s="2" t="n">
         <v>146</v>
       </c>
@@ -5441,7 +5491,7 @@
         </is>
       </c>
     </row>
-    <row r="148">
+    <row r="148" ht="28" customHeight="1">
       <c r="A148" s="2" t="n">
         <v>147</v>
       </c>
@@ -5475,7 +5525,7 @@
         </is>
       </c>
     </row>
-    <row r="149">
+    <row r="149" ht="28" customHeight="1">
       <c r="A149" s="2" t="n">
         <v>148</v>
       </c>
@@ -5509,7 +5559,7 @@
         </is>
       </c>
     </row>
-    <row r="150">
+    <row r="150" ht="28" customHeight="1">
       <c r="A150" s="2" t="n">
         <v>149</v>
       </c>
@@ -5543,7 +5593,7 @@
         </is>
       </c>
     </row>
-    <row r="151">
+    <row r="151" ht="28" customHeight="1">
       <c r="A151" s="2" t="n">
         <v>150</v>
       </c>
@@ -5577,7 +5627,7 @@
         </is>
       </c>
     </row>
-    <row r="152">
+    <row r="152" ht="28" customHeight="1">
       <c r="A152" s="2" t="n">
         <v>151</v>
       </c>
@@ -5611,7 +5661,7 @@
         </is>
       </c>
     </row>
-    <row r="153">
+    <row r="153" ht="28" customHeight="1">
       <c r="A153" s="2" t="n">
         <v>152</v>
       </c>
@@ -5645,7 +5695,7 @@
         </is>
       </c>
     </row>
-    <row r="154">
+    <row r="154" ht="28" customHeight="1">
       <c r="A154" s="2" t="n">
         <v>153</v>
       </c>
@@ -5679,7 +5729,7 @@
         </is>
       </c>
     </row>
-    <row r="155">
+    <row r="155" ht="28" customHeight="1">
       <c r="A155" s="2" t="n">
         <v>154</v>
       </c>
@@ -5713,7 +5763,7 @@
         </is>
       </c>
     </row>
-    <row r="156">
+    <row r="156" ht="28" customHeight="1">
       <c r="A156" s="2" t="n">
         <v>155</v>
       </c>
@@ -5747,7 +5797,7 @@
         </is>
       </c>
     </row>
-    <row r="157">
+    <row r="157" ht="28" customHeight="1">
       <c r="A157" s="2" t="n">
         <v>156</v>
       </c>
@@ -5781,7 +5831,7 @@
         </is>
       </c>
     </row>
-    <row r="158">
+    <row r="158" ht="28" customHeight="1">
       <c r="A158" s="2" t="n">
         <v>157</v>
       </c>
@@ -5815,7 +5865,7 @@
         </is>
       </c>
     </row>
-    <row r="159">
+    <row r="159" ht="28" customHeight="1">
       <c r="A159" s="2" t="n">
         <v>158</v>
       </c>
@@ -5849,7 +5899,7 @@
         </is>
       </c>
     </row>
-    <row r="160">
+    <row r="160" ht="28" customHeight="1">
       <c r="A160" s="2" t="n">
         <v>159</v>
       </c>
@@ -5883,7 +5933,7 @@
         </is>
       </c>
     </row>
-    <row r="161">
+    <row r="161" ht="28" customHeight="1">
       <c r="A161" s="2" t="n">
         <v>160</v>
       </c>
@@ -5917,7 +5967,7 @@
         </is>
       </c>
     </row>
-    <row r="162">
+    <row r="162" ht="28" customHeight="1">
       <c r="A162" s="2" t="n">
         <v>161</v>
       </c>
@@ -5951,7 +6001,7 @@
         </is>
       </c>
     </row>
-    <row r="163">
+    <row r="163" ht="28" customHeight="1">
       <c r="A163" s="2" t="n">
         <v>162</v>
       </c>
@@ -5985,7 +6035,7 @@
         </is>
       </c>
     </row>
-    <row r="164">
+    <row r="164" ht="28" customHeight="1">
       <c r="A164" s="2" t="n">
         <v>163</v>
       </c>
@@ -6019,7 +6069,7 @@
         </is>
       </c>
     </row>
-    <row r="165">
+    <row r="165" ht="28" customHeight="1">
       <c r="A165" s="2" t="n">
         <v>164</v>
       </c>
@@ -6053,7 +6103,7 @@
         </is>
       </c>
     </row>
-    <row r="166">
+    <row r="166" ht="28" customHeight="1">
       <c r="A166" s="2" t="n">
         <v>165</v>
       </c>
@@ -6087,7 +6137,7 @@
         </is>
       </c>
     </row>
-    <row r="167">
+    <row r="167" ht="28" customHeight="1">
       <c r="A167" s="2" t="n">
         <v>166</v>
       </c>
@@ -6121,7 +6171,7 @@
         </is>
       </c>
     </row>
-    <row r="168">
+    <row r="168" ht="28" customHeight="1">
       <c r="A168" s="2" t="n">
         <v>167</v>
       </c>
@@ -6155,7 +6205,7 @@
         </is>
       </c>
     </row>
-    <row r="169">
+    <row r="169" ht="28" customHeight="1">
       <c r="A169" s="2" t="n">
         <v>168</v>
       </c>
@@ -6189,7 +6239,7 @@
         </is>
       </c>
     </row>
-    <row r="170">
+    <row r="170" ht="28" customHeight="1">
       <c r="A170" s="2" t="n">
         <v>169</v>
       </c>
@@ -6223,7 +6273,7 @@
         </is>
       </c>
     </row>
-    <row r="171">
+    <row r="171" ht="28" customHeight="1">
       <c r="A171" s="2" t="n">
         <v>170</v>
       </c>
@@ -6257,7 +6307,7 @@
         </is>
       </c>
     </row>
-    <row r="172">
+    <row r="172" ht="28" customHeight="1">
       <c r="A172" s="2" t="n">
         <v>171</v>
       </c>
@@ -6291,7 +6341,7 @@
         </is>
       </c>
     </row>
-    <row r="173">
+    <row r="173" ht="28" customHeight="1">
       <c r="A173" s="2" t="n">
         <v>172</v>
       </c>
@@ -6325,7 +6375,7 @@
         </is>
       </c>
     </row>
-    <row r="174">
+    <row r="174" ht="28" customHeight="1">
       <c r="A174" s="2" t="n">
         <v>173</v>
       </c>
@@ -6359,7 +6409,7 @@
         </is>
       </c>
     </row>
-    <row r="175">
+    <row r="175" ht="28" customHeight="1">
       <c r="A175" s="2" t="n">
         <v>174</v>
       </c>
@@ -6393,7 +6443,7 @@
         </is>
       </c>
     </row>
-    <row r="176">
+    <row r="176" ht="28" customHeight="1">
       <c r="A176" s="2" t="n">
         <v>175</v>
       </c>
@@ -6427,7 +6477,7 @@
         </is>
       </c>
     </row>
-    <row r="177">
+    <row r="177" ht="28" customHeight="1">
       <c r="A177" s="2" t="n">
         <v>176</v>
       </c>
@@ -6461,7 +6511,7 @@
         </is>
       </c>
     </row>
-    <row r="178">
+    <row r="178" ht="28" customHeight="1">
       <c r="A178" s="2" t="n">
         <v>177</v>
       </c>
@@ -6495,7 +6545,7 @@
         </is>
       </c>
     </row>
-    <row r="179">
+    <row r="179" ht="28" customHeight="1">
       <c r="A179" s="2" t="n">
         <v>178</v>
       </c>
@@ -6529,7 +6579,7 @@
         </is>
       </c>
     </row>
-    <row r="180">
+    <row r="180" ht="28" customHeight="1">
       <c r="A180" s="2" t="n">
         <v>179</v>
       </c>
@@ -6563,7 +6613,7 @@
         </is>
       </c>
     </row>
-    <row r="181">
+    <row r="181" ht="28" customHeight="1">
       <c r="A181" s="2" t="n">
         <v>180</v>
       </c>
@@ -6597,7 +6647,7 @@
         </is>
       </c>
     </row>
-    <row r="182">
+    <row r="182" ht="28" customHeight="1">
       <c r="A182" s="2" t="n">
         <v>181</v>
       </c>
@@ -6631,7 +6681,7 @@
         </is>
       </c>
     </row>
-    <row r="183">
+    <row r="183" ht="28" customHeight="1">
       <c r="A183" s="2" t="n">
         <v>182</v>
       </c>
@@ -6665,7 +6715,7 @@
         </is>
       </c>
     </row>
-    <row r="184">
+    <row r="184" ht="28" customHeight="1">
       <c r="A184" s="2" t="n">
         <v>183</v>
       </c>
@@ -6699,7 +6749,7 @@
         </is>
       </c>
     </row>
-    <row r="185">
+    <row r="185" ht="28" customHeight="1">
       <c r="A185" s="2" t="n">
         <v>184</v>
       </c>
@@ -6733,7 +6783,7 @@
         </is>
       </c>
     </row>
-    <row r="186">
+    <row r="186" ht="28" customHeight="1">
       <c r="A186" s="2" t="n">
         <v>185</v>
       </c>
@@ -6767,7 +6817,7 @@
         </is>
       </c>
     </row>
-    <row r="187">
+    <row r="187" ht="28" customHeight="1">
       <c r="A187" s="2" t="n">
         <v>186</v>
       </c>
@@ -6801,7 +6851,7 @@
         </is>
       </c>
     </row>
-    <row r="188">
+    <row r="188" ht="28" customHeight="1">
       <c r="A188" s="2" t="n">
         <v>187</v>
       </c>
@@ -6835,7 +6885,7 @@
         </is>
       </c>
     </row>
-    <row r="189">
+    <row r="189" ht="28" customHeight="1">
       <c r="A189" s="2" t="n">
         <v>188</v>
       </c>
@@ -6869,7 +6919,7 @@
         </is>
       </c>
     </row>
-    <row r="190">
+    <row r="190" ht="28" customHeight="1">
       <c r="A190" s="2" t="n">
         <v>189</v>
       </c>
@@ -6903,7 +6953,7 @@
         </is>
       </c>
     </row>
-    <row r="191">
+    <row r="191" ht="28" customHeight="1">
       <c r="A191" s="2" t="n">
         <v>190</v>
       </c>
@@ -6937,7 +6987,7 @@
         </is>
       </c>
     </row>
-    <row r="192">
+    <row r="192" ht="28" customHeight="1">
       <c r="A192" s="2" t="n">
         <v>191</v>
       </c>
@@ -6971,7 +7021,7 @@
         </is>
       </c>
     </row>
-    <row r="193">
+    <row r="193" ht="28" customHeight="1">
       <c r="A193" s="2" t="n">
         <v>192</v>
       </c>
@@ -7005,7 +7055,7 @@
         </is>
       </c>
     </row>
-    <row r="194">
+    <row r="194" ht="28" customHeight="1">
       <c r="A194" s="2" t="n">
         <v>193</v>
       </c>
@@ -7039,7 +7089,7 @@
         </is>
       </c>
     </row>
-    <row r="195">
+    <row r="195" ht="28" customHeight="1">
       <c r="A195" s="2" t="n">
         <v>194</v>
       </c>
@@ -7073,7 +7123,7 @@
         </is>
       </c>
     </row>
-    <row r="196">
+    <row r="196" ht="28" customHeight="1">
       <c r="A196" s="2" t="n">
         <v>195</v>
       </c>
@@ -7107,7 +7157,7 @@
         </is>
       </c>
     </row>
-    <row r="197">
+    <row r="197" ht="28" customHeight="1">
       <c r="A197" s="2" t="n">
         <v>196</v>
       </c>
@@ -7141,7 +7191,7 @@
         </is>
       </c>
     </row>
-    <row r="198">
+    <row r="198" ht="28" customHeight="1">
       <c r="A198" s="2" t="n">
         <v>197</v>
       </c>
@@ -7175,7 +7225,7 @@
         </is>
       </c>
     </row>
-    <row r="199">
+    <row r="199" ht="28" customHeight="1">
       <c r="A199" s="2" t="n">
         <v>198</v>
       </c>
@@ -7209,7 +7259,7 @@
         </is>
       </c>
     </row>
-    <row r="200">
+    <row r="200" ht="28" customHeight="1">
       <c r="A200" s="2" t="n">
         <v>199</v>
       </c>
@@ -7243,7 +7293,7 @@
         </is>
       </c>
     </row>
-    <row r="201">
+    <row r="201" ht="28" customHeight="1">
       <c r="A201" s="2" t="n">
         <v>200</v>
       </c>
@@ -7277,7 +7327,7 @@
         </is>
       </c>
     </row>
-    <row r="202">
+    <row r="202" ht="28" customHeight="1">
       <c r="A202" s="2" t="n">
         <v>201</v>
       </c>
@@ -7311,7 +7361,7 @@
         </is>
       </c>
     </row>
-    <row r="203">
+    <row r="203" ht="28" customHeight="1">
       <c r="A203" s="2" t="n">
         <v>202</v>
       </c>
@@ -7345,7 +7395,7 @@
         </is>
       </c>
     </row>
-    <row r="204">
+    <row r="204" ht="28" customHeight="1">
       <c r="A204" s="2" t="n">
         <v>203</v>
       </c>
@@ -7379,7 +7429,7 @@
         </is>
       </c>
     </row>
-    <row r="205">
+    <row r="205" ht="28" customHeight="1">
       <c r="A205" s="2" t="n">
         <v>204</v>
       </c>
@@ -7413,7 +7463,7 @@
         </is>
       </c>
     </row>
-    <row r="206">
+    <row r="206" ht="28" customHeight="1">
       <c r="A206" s="2" t="n">
         <v>205</v>
       </c>
@@ -7447,7 +7497,7 @@
         </is>
       </c>
     </row>
-    <row r="207">
+    <row r="207" ht="28" customHeight="1">
       <c r="A207" s="2" t="n">
         <v>206</v>
       </c>
@@ -7481,7 +7531,7 @@
         </is>
       </c>
     </row>
-    <row r="208">
+    <row r="208" ht="28" customHeight="1">
       <c r="A208" s="2" t="n">
         <v>207</v>
       </c>
@@ -7515,7 +7565,7 @@
         </is>
       </c>
     </row>
-    <row r="209">
+    <row r="209" ht="28" customHeight="1">
       <c r="A209" s="2" t="n">
         <v>208</v>
       </c>
@@ -7549,7 +7599,7 @@
         </is>
       </c>
     </row>
-    <row r="210">
+    <row r="210" ht="28" customHeight="1">
       <c r="A210" s="2" t="n">
         <v>209</v>
       </c>
@@ -7583,7 +7633,7 @@
         </is>
       </c>
     </row>
-    <row r="211">
+    <row r="211" ht="28" customHeight="1">
       <c r="A211" s="2" t="n">
         <v>210</v>
       </c>
@@ -7617,7 +7667,7 @@
         </is>
       </c>
     </row>
-    <row r="212">
+    <row r="212" ht="28" customHeight="1">
       <c r="A212" s="2" t="n">
         <v>211</v>
       </c>
@@ -7651,7 +7701,7 @@
         </is>
       </c>
     </row>
-    <row r="213">
+    <row r="213" ht="28" customHeight="1">
       <c r="A213" s="2" t="n">
         <v>212</v>
       </c>
@@ -7685,7 +7735,7 @@
         </is>
       </c>
     </row>
-    <row r="214">
+    <row r="214" ht="28" customHeight="1">
       <c r="A214" s="2" t="n">
         <v>213</v>
       </c>
@@ -7719,7 +7769,7 @@
         </is>
       </c>
     </row>
-    <row r="215">
+    <row r="215" ht="28" customHeight="1">
       <c r="A215" s="2" t="n">
         <v>214</v>
       </c>
@@ -7753,7 +7803,7 @@
         </is>
       </c>
     </row>
-    <row r="216">
+    <row r="216" ht="28" customHeight="1">
       <c r="A216" s="2" t="n">
         <v>215</v>
       </c>
@@ -7787,7 +7837,7 @@
         </is>
       </c>
     </row>
-    <row r="217">
+    <row r="217" ht="28" customHeight="1">
       <c r="A217" s="2" t="n">
         <v>216</v>
       </c>
@@ -7821,7 +7871,7 @@
         </is>
       </c>
     </row>
-    <row r="218">
+    <row r="218" ht="28" customHeight="1">
       <c r="A218" s="2" t="n">
         <v>217</v>
       </c>
@@ -7855,7 +7905,7 @@
         </is>
       </c>
     </row>
-    <row r="219">
+    <row r="219" ht="28" customHeight="1">
       <c r="A219" s="2" t="n">
         <v>218</v>
       </c>
@@ -7889,7 +7939,7 @@
         </is>
       </c>
     </row>
-    <row r="220">
+    <row r="220" ht="28" customHeight="1">
       <c r="A220" s="2" t="n">
         <v>219</v>
       </c>
@@ -7923,7 +7973,7 @@
         </is>
       </c>
     </row>
-    <row r="221">
+    <row r="221" ht="28" customHeight="1">
       <c r="A221" s="2" t="n">
         <v>220</v>
       </c>
@@ -7957,7 +8007,7 @@
         </is>
       </c>
     </row>
-    <row r="222">
+    <row r="222" ht="28" customHeight="1">
       <c r="A222" s="2" t="n">
         <v>221</v>
       </c>
@@ -7991,7 +8041,7 @@
         </is>
       </c>
     </row>
-    <row r="223">
+    <row r="223" ht="28" customHeight="1">
       <c r="A223" s="2" t="n">
         <v>222</v>
       </c>
@@ -8025,7 +8075,7 @@
         </is>
       </c>
     </row>
-    <row r="224">
+    <row r="224" ht="28" customHeight="1">
       <c r="A224" s="2" t="n">
         <v>223</v>
       </c>
@@ -8059,7 +8109,7 @@
         </is>
       </c>
     </row>
-    <row r="225">
+    <row r="225" ht="28" customHeight="1">
       <c r="A225" s="2" t="n">
         <v>224</v>
       </c>
@@ -8093,7 +8143,7 @@
         </is>
       </c>
     </row>
-    <row r="226">
+    <row r="226" ht="28" customHeight="1">
       <c r="A226" s="2" t="n">
         <v>225</v>
       </c>
@@ -8127,7 +8177,7 @@
         </is>
       </c>
     </row>
-    <row r="227">
+    <row r="227" ht="28" customHeight="1">
       <c r="A227" s="2" t="n">
         <v>226</v>
       </c>
@@ -8161,7 +8211,7 @@
         </is>
       </c>
     </row>
-    <row r="228">
+    <row r="228" ht="28" customHeight="1">
       <c r="A228" s="2" t="n">
         <v>227</v>
       </c>
@@ -8195,7 +8245,7 @@
         </is>
       </c>
     </row>
-    <row r="229">
+    <row r="229" ht="28" customHeight="1">
       <c r="A229" s="2" t="n">
         <v>228</v>
       </c>
@@ -8229,7 +8279,7 @@
         </is>
       </c>
     </row>
-    <row r="230">
+    <row r="230" ht="28" customHeight="1">
       <c r="A230" s="2" t="n">
         <v>229</v>
       </c>
@@ -8263,7 +8313,7 @@
         </is>
       </c>
     </row>
-    <row r="231">
+    <row r="231" ht="28" customHeight="1">
       <c r="A231" s="2" t="n">
         <v>230</v>
       </c>
@@ -8297,7 +8347,7 @@
         </is>
       </c>
     </row>
-    <row r="232">
+    <row r="232" ht="28" customHeight="1">
       <c r="A232" s="2" t="n">
         <v>231</v>
       </c>
@@ -8331,7 +8381,7 @@
         </is>
       </c>
     </row>
-    <row r="233">
+    <row r="233" ht="28" customHeight="1">
       <c r="A233" s="2" t="n">
         <v>232</v>
       </c>
@@ -8365,7 +8415,7 @@
         </is>
       </c>
     </row>
-    <row r="234">
+    <row r="234" ht="28" customHeight="1">
       <c r="A234" s="2" t="n">
         <v>233</v>
       </c>
@@ -8399,7 +8449,7 @@
         </is>
       </c>
     </row>
-    <row r="235">
+    <row r="235" ht="28" customHeight="1">
       <c r="A235" s="2" t="n">
         <v>234</v>
       </c>
@@ -8433,7 +8483,7 @@
         </is>
       </c>
     </row>
-    <row r="236">
+    <row r="236" ht="28" customHeight="1">
       <c r="A236" s="2" t="n">
         <v>235</v>
       </c>
@@ -8467,7 +8517,7 @@
         </is>
       </c>
     </row>
-    <row r="237">
+    <row r="237" ht="28" customHeight="1">
       <c r="A237" s="2" t="n">
         <v>236</v>
       </c>
@@ -8501,7 +8551,7 @@
         </is>
       </c>
     </row>
-    <row r="238">
+    <row r="238" ht="28" customHeight="1">
       <c r="A238" s="2" t="n">
         <v>237</v>
       </c>
@@ -8535,7 +8585,7 @@
         </is>
       </c>
     </row>
-    <row r="239">
+    <row r="239" ht="28" customHeight="1">
       <c r="A239" s="2" t="n">
         <v>238</v>
       </c>
@@ -8569,7 +8619,7 @@
         </is>
       </c>
     </row>
-    <row r="240">
+    <row r="240" ht="28" customHeight="1">
       <c r="A240" s="2" t="n">
         <v>239</v>
       </c>
@@ -8603,7 +8653,7 @@
         </is>
       </c>
     </row>
-    <row r="241">
+    <row r="241" ht="28" customHeight="1">
       <c r="A241" s="2" t="n">
         <v>240</v>
       </c>
@@ -8637,7 +8687,7 @@
         </is>
       </c>
     </row>
-    <row r="242">
+    <row r="242" ht="28" customHeight="1">
       <c r="A242" s="2" t="n">
         <v>241</v>
       </c>
@@ -8671,7 +8721,7 @@
         </is>
       </c>
     </row>
-    <row r="243">
+    <row r="243" ht="28" customHeight="1">
       <c r="A243" s="2" t="n">
         <v>242</v>
       </c>
@@ -8705,7 +8755,7 @@
         </is>
       </c>
     </row>
-    <row r="244">
+    <row r="244" ht="28" customHeight="1">
       <c r="A244" s="2" t="n">
         <v>243</v>
       </c>
@@ -8739,7 +8789,7 @@
         </is>
       </c>
     </row>
-    <row r="245">
+    <row r="245" ht="28" customHeight="1">
       <c r="A245" s="2" t="n">
         <v>244</v>
       </c>
@@ -8773,7 +8823,7 @@
         </is>
       </c>
     </row>
-    <row r="246">
+    <row r="246" ht="28" customHeight="1">
       <c r="A246" s="2" t="n">
         <v>245</v>
       </c>
@@ -8807,7 +8857,7 @@
         </is>
       </c>
     </row>
-    <row r="247">
+    <row r="247" ht="28" customHeight="1">
       <c r="A247" s="2" t="n">
         <v>246</v>
       </c>
@@ -8841,7 +8891,7 @@
         </is>
       </c>
     </row>
-    <row r="248">
+    <row r="248" ht="28" customHeight="1">
       <c r="A248" s="2" t="n">
         <v>247</v>
       </c>
@@ -8875,7 +8925,7 @@
         </is>
       </c>
     </row>
-    <row r="249">
+    <row r="249" ht="28" customHeight="1">
       <c r="A249" s="2" t="n">
         <v>248</v>
       </c>
@@ -8909,7 +8959,7 @@
         </is>
       </c>
     </row>
-    <row r="250">
+    <row r="250" ht="28" customHeight="1">
       <c r="A250" s="2" t="n">
         <v>249</v>
       </c>
@@ -8943,7 +8993,7 @@
         </is>
       </c>
     </row>
-    <row r="251">
+    <row r="251" ht="28" customHeight="1">
       <c r="A251" s="2" t="n">
         <v>250</v>
       </c>
@@ -8977,7 +9027,7 @@
         </is>
       </c>
     </row>
-    <row r="252">
+    <row r="252" ht="28" customHeight="1">
       <c r="A252" s="2" t="n">
         <v>251</v>
       </c>
@@ -9011,7 +9061,7 @@
         </is>
       </c>
     </row>
-    <row r="253">
+    <row r="253" ht="28" customHeight="1">
       <c r="A253" s="2" t="n">
         <v>252</v>
       </c>
@@ -9045,7 +9095,7 @@
         </is>
       </c>
     </row>
-    <row r="254">
+    <row r="254" ht="28" customHeight="1">
       <c r="A254" s="2" t="n">
         <v>253</v>
       </c>
@@ -9079,7 +9129,7 @@
         </is>
       </c>
     </row>
-    <row r="255">
+    <row r="255" ht="28" customHeight="1">
       <c r="A255" s="2" t="n">
         <v>254</v>
       </c>
@@ -9113,7 +9163,7 @@
         </is>
       </c>
     </row>
-    <row r="256">
+    <row r="256" ht="28" customHeight="1">
       <c r="A256" s="2" t="n">
         <v>255</v>
       </c>
@@ -9147,7 +9197,7 @@
         </is>
       </c>
     </row>
-    <row r="257">
+    <row r="257" ht="28" customHeight="1">
       <c r="A257" s="2" t="n">
         <v>256</v>
       </c>
@@ -9181,7 +9231,7 @@
         </is>
       </c>
     </row>
-    <row r="258">
+    <row r="258" ht="28" customHeight="1">
       <c r="A258" s="2" t="n">
         <v>257</v>
       </c>
@@ -9215,7 +9265,7 @@
         </is>
       </c>
     </row>
-    <row r="259">
+    <row r="259" ht="28" customHeight="1">
       <c r="A259" s="2" t="n">
         <v>258</v>
       </c>
@@ -9249,7 +9299,7 @@
         </is>
       </c>
     </row>
-    <row r="260">
+    <row r="260" ht="28" customHeight="1">
       <c r="A260" s="2" t="n">
         <v>259</v>
       </c>
@@ -9283,7 +9333,7 @@
         </is>
       </c>
     </row>
-    <row r="261">
+    <row r="261" ht="28" customHeight="1">
       <c r="A261" s="2" t="n">
         <v>260</v>
       </c>
@@ -9317,7 +9367,7 @@
         </is>
       </c>
     </row>
-    <row r="262">
+    <row r="262" ht="28" customHeight="1">
       <c r="A262" s="2" t="n">
         <v>261</v>
       </c>
@@ -9351,7 +9401,7 @@
         </is>
       </c>
     </row>
-    <row r="263">
+    <row r="263" ht="28" customHeight="1">
       <c r="A263" s="2" t="n">
         <v>262</v>
       </c>
@@ -9385,7 +9435,7 @@
         </is>
       </c>
     </row>
-    <row r="264">
+    <row r="264" ht="28" customHeight="1">
       <c r="A264" s="2" t="n">
         <v>263</v>
       </c>
@@ -9419,7 +9469,7 @@
         </is>
       </c>
     </row>
-    <row r="265">
+    <row r="265" ht="28" customHeight="1">
       <c r="A265" s="2" t="n">
         <v>264</v>
       </c>
@@ -9453,7 +9503,7 @@
         </is>
       </c>
     </row>
-    <row r="266">
+    <row r="266" ht="28" customHeight="1">
       <c r="A266" s="2" t="n">
         <v>265</v>
       </c>
@@ -9487,7 +9537,7 @@
         </is>
       </c>
     </row>
-    <row r="267">
+    <row r="267" ht="28" customHeight="1">
       <c r="A267" s="2" t="n">
         <v>266</v>
       </c>
@@ -9521,7 +9571,7 @@
         </is>
       </c>
     </row>
-    <row r="268">
+    <row r="268" ht="28" customHeight="1">
       <c r="A268" s="2" t="n">
         <v>267</v>
       </c>
@@ -9555,7 +9605,7 @@
         </is>
       </c>
     </row>
-    <row r="269">
+    <row r="269" ht="28" customHeight="1">
       <c r="A269" s="2" t="n">
         <v>268</v>
       </c>
@@ -9589,7 +9639,7 @@
         </is>
       </c>
     </row>
-    <row r="270">
+    <row r="270" ht="28" customHeight="1">
       <c r="A270" s="2" t="n">
         <v>269</v>
       </c>
@@ -9623,7 +9673,7 @@
         </is>
       </c>
     </row>
-    <row r="271">
+    <row r="271" ht="28" customHeight="1">
       <c r="A271" s="2" t="n">
         <v>270</v>
       </c>
@@ -9657,7 +9707,7 @@
         </is>
       </c>
     </row>
-    <row r="272">
+    <row r="272" ht="28" customHeight="1">
       <c r="A272" s="2" t="n">
         <v>271</v>
       </c>
@@ -9691,7 +9741,7 @@
         </is>
       </c>
     </row>
-    <row r="273">
+    <row r="273" ht="28" customHeight="1">
       <c r="A273" s="2" t="n">
         <v>272</v>
       </c>
@@ -9725,7 +9775,7 @@
         </is>
       </c>
     </row>
-    <row r="274">
+    <row r="274" ht="28" customHeight="1">
       <c r="A274" s="2" t="n">
         <v>273</v>
       </c>
@@ -9759,7 +9809,7 @@
         </is>
       </c>
     </row>
-    <row r="275">
+    <row r="275" ht="28" customHeight="1">
       <c r="A275" s="2" t="n">
         <v>274</v>
       </c>
@@ -9793,7 +9843,7 @@
         </is>
       </c>
     </row>
-    <row r="276">
+    <row r="276" ht="28" customHeight="1">
       <c r="A276" s="2" t="n">
         <v>275</v>
       </c>
@@ -9827,7 +9877,7 @@
         </is>
       </c>
     </row>
-    <row r="277">
+    <row r="277" ht="28" customHeight="1">
       <c r="A277" s="2" t="n">
         <v>276</v>
       </c>
@@ -9861,7 +9911,7 @@
         </is>
       </c>
     </row>
-    <row r="278">
+    <row r="278" ht="28" customHeight="1">
       <c r="A278" s="2" t="n">
         <v>277</v>
       </c>
@@ -9895,7 +9945,7 @@
         </is>
       </c>
     </row>
-    <row r="279">
+    <row r="279" ht="28" customHeight="1">
       <c r="A279" s="2" t="n">
         <v>278</v>
       </c>
@@ -9929,7 +9979,7 @@
         </is>
       </c>
     </row>
-    <row r="280">
+    <row r="280" ht="28" customHeight="1">
       <c r="A280" s="2" t="n">
         <v>279</v>
       </c>
@@ -9963,7 +10013,7 @@
         </is>
       </c>
     </row>
-    <row r="281">
+    <row r="281" ht="28" customHeight="1">
       <c r="A281" s="2" t="n">
         <v>280</v>
       </c>
@@ -9997,7 +10047,7 @@
         </is>
       </c>
     </row>
-    <row r="282">
+    <row r="282" ht="28" customHeight="1">
       <c r="A282" s="2" t="n">
         <v>281</v>
       </c>
@@ -10031,7 +10081,7 @@
         </is>
       </c>
     </row>
-    <row r="283">
+    <row r="283" ht="28" customHeight="1">
       <c r="A283" s="2" t="n">
         <v>282</v>
       </c>
@@ -10065,7 +10115,7 @@
         </is>
       </c>
     </row>
-    <row r="284">
+    <row r="284" ht="28" customHeight="1">
       <c r="A284" s="2" t="n">
         <v>283</v>
       </c>
@@ -10099,7 +10149,7 @@
         </is>
       </c>
     </row>
-    <row r="285">
+    <row r="285" ht="28" customHeight="1">
       <c r="A285" s="2" t="n">
         <v>284</v>
       </c>
@@ -10133,7 +10183,7 @@
         </is>
       </c>
     </row>
-    <row r="286">
+    <row r="286" ht="28" customHeight="1">
       <c r="A286" s="2" t="n">
         <v>285</v>
       </c>
@@ -10167,7 +10217,7 @@
         </is>
       </c>
     </row>
-    <row r="287">
+    <row r="287" ht="28" customHeight="1">
       <c r="A287" s="2" t="n">
         <v>286</v>
       </c>
@@ -10201,7 +10251,7 @@
         </is>
       </c>
     </row>
-    <row r="288">
+    <row r="288" ht="28" customHeight="1">
       <c r="A288" s="2" t="n">
         <v>287</v>
       </c>
@@ -10235,7 +10285,7 @@
         </is>
       </c>
     </row>
-    <row r="289">
+    <row r="289" ht="28" customHeight="1">
       <c r="A289" s="2" t="n">
         <v>288</v>
       </c>
@@ -10269,7 +10319,7 @@
         </is>
       </c>
     </row>
-    <row r="290">
+    <row r="290" ht="28" customHeight="1">
       <c r="A290" s="2" t="n">
         <v>289</v>
       </c>
@@ -10303,7 +10353,7 @@
         </is>
       </c>
     </row>
-    <row r="291">
+    <row r="291" ht="28" customHeight="1">
       <c r="A291" s="2" t="n">
         <v>290</v>
       </c>
@@ -10337,7 +10387,7 @@
         </is>
       </c>
     </row>
-    <row r="292">
+    <row r="292" ht="28" customHeight="1">
       <c r="A292" s="2" t="n">
         <v>291</v>
       </c>
@@ -10371,7 +10421,7 @@
         </is>
       </c>
     </row>
-    <row r="293">
+    <row r="293" ht="28" customHeight="1">
       <c r="A293" s="2" t="n">
         <v>292</v>
       </c>
@@ -10405,7 +10455,7 @@
         </is>
       </c>
     </row>
-    <row r="294">
+    <row r="294" ht="28" customHeight="1">
       <c r="A294" s="2" t="n">
         <v>293</v>
       </c>
@@ -10439,7 +10489,7 @@
         </is>
       </c>
     </row>
-    <row r="295">
+    <row r="295" ht="28" customHeight="1">
       <c r="A295" s="2" t="n">
         <v>294</v>
       </c>
@@ -10473,7 +10523,7 @@
         </is>
       </c>
     </row>
-    <row r="296">
+    <row r="296" ht="28" customHeight="1">
       <c r="A296" s="2" t="n">
         <v>295</v>
       </c>
@@ -10507,7 +10557,7 @@
         </is>
       </c>
     </row>
-    <row r="297">
+    <row r="297" ht="28" customHeight="1">
       <c r="A297" s="2" t="n">
         <v>296</v>
       </c>
@@ -10541,7 +10591,7 @@
         </is>
       </c>
     </row>
-    <row r="298">
+    <row r="298" ht="28" customHeight="1">
       <c r="A298" s="2" t="n">
         <v>297</v>
       </c>
@@ -10575,7 +10625,7 @@
         </is>
       </c>
     </row>
-    <row r="299">
+    <row r="299" ht="28" customHeight="1">
       <c r="A299" s="2" t="n">
         <v>298</v>
       </c>
@@ -10609,7 +10659,7 @@
         </is>
       </c>
     </row>
-    <row r="300">
+    <row r="300" ht="28" customHeight="1">
       <c r="A300" s="2" t="n">
         <v>299</v>
       </c>
@@ -10643,7 +10693,7 @@
         </is>
       </c>
     </row>
-    <row r="301">
+    <row r="301" ht="28" customHeight="1">
       <c r="A301" s="2" t="n">
         <v>300</v>
       </c>
@@ -10677,7 +10727,7 @@
         </is>
       </c>
     </row>
-    <row r="302">
+    <row r="302" ht="28" customHeight="1">
       <c r="A302" s="2" t="n">
         <v>301</v>
       </c>
@@ -10711,7 +10761,7 @@
         </is>
       </c>
     </row>
-    <row r="303">
+    <row r="303" ht="28" customHeight="1">
       <c r="A303" s="2" t="n">
         <v>302</v>
       </c>
@@ -10745,7 +10795,7 @@
         </is>
       </c>
     </row>
-    <row r="304">
+    <row r="304" ht="28" customHeight="1">
       <c r="A304" s="2" t="n">
         <v>303</v>
       </c>
@@ -10779,7 +10829,7 @@
         </is>
       </c>
     </row>
-    <row r="305">
+    <row r="305" ht="28" customHeight="1">
       <c r="A305" s="2" t="n">
         <v>304</v>
       </c>
@@ -10813,7 +10863,7 @@
         </is>
       </c>
     </row>
-    <row r="306">
+    <row r="306" ht="28" customHeight="1">
       <c r="A306" s="2" t="n">
         <v>305</v>
       </c>
@@ -10847,7 +10897,7 @@
         </is>
       </c>
     </row>
-    <row r="307">
+    <row r="307" ht="28" customHeight="1">
       <c r="A307" s="2" t="n">
         <v>306</v>
       </c>
@@ -10881,7 +10931,7 @@
         </is>
       </c>
     </row>
-    <row r="308">
+    <row r="308" ht="28" customHeight="1">
       <c r="A308" s="2" t="n">
         <v>307</v>
       </c>
@@ -10915,7 +10965,7 @@
         </is>
       </c>
     </row>
-    <row r="309">
+    <row r="309" ht="28" customHeight="1">
       <c r="A309" s="2" t="n">
         <v>308</v>
       </c>
@@ -10949,7 +10999,7 @@
         </is>
       </c>
     </row>
-    <row r="310">
+    <row r="310" ht="28" customHeight="1">
       <c r="A310" s="2" t="n">
         <v>309</v>
       </c>
@@ -10983,7 +11033,7 @@
         </is>
       </c>
     </row>
-    <row r="311">
+    <row r="311" ht="28" customHeight="1">
       <c r="A311" s="2" t="n">
         <v>310</v>
       </c>
@@ -11017,7 +11067,7 @@
         </is>
       </c>
     </row>
-    <row r="312">
+    <row r="312" ht="28" customHeight="1">
       <c r="A312" s="2" t="n">
         <v>311</v>
       </c>
@@ -11051,7 +11101,7 @@
         </is>
       </c>
     </row>
-    <row r="313">
+    <row r="313" ht="28" customHeight="1">
       <c r="A313" s="2" t="n">
         <v>312</v>
       </c>
@@ -11085,7 +11135,7 @@
         </is>
       </c>
     </row>
-    <row r="314">
+    <row r="314" ht="28" customHeight="1">
       <c r="A314" s="2" t="n">
         <v>313</v>
       </c>
@@ -11119,7 +11169,7 @@
         </is>
       </c>
     </row>
-    <row r="315">
+    <row r="315" ht="28" customHeight="1">
       <c r="A315" s="2" t="n">
         <v>314</v>
       </c>
@@ -11153,7 +11203,7 @@
         </is>
       </c>
     </row>
-    <row r="316">
+    <row r="316" ht="28" customHeight="1">
       <c r="A316" s="2" t="n">
         <v>315</v>
       </c>
@@ -11187,7 +11237,7 @@
         </is>
       </c>
     </row>
-    <row r="317">
+    <row r="317" ht="28" customHeight="1">
       <c r="A317" s="2" t="n">
         <v>316</v>
       </c>
@@ -11221,7 +11271,7 @@
         </is>
       </c>
     </row>
-    <row r="318">
+    <row r="318" ht="28" customHeight="1">
       <c r="A318" s="2" t="n">
         <v>317</v>
       </c>
@@ -11255,7 +11305,7 @@
         </is>
       </c>
     </row>
-    <row r="319">
+    <row r="319" ht="28" customHeight="1">
       <c r="A319" s="2" t="n">
         <v>318</v>
       </c>
@@ -11289,7 +11339,7 @@
         </is>
       </c>
     </row>
-    <row r="320">
+    <row r="320" ht="28" customHeight="1">
       <c r="A320" s="2" t="n">
         <v>319</v>
       </c>
@@ -11323,7 +11373,7 @@
         </is>
       </c>
     </row>
-    <row r="321">
+    <row r="321" ht="28" customHeight="1">
       <c r="A321" s="2" t="n">
         <v>320</v>
       </c>
@@ -11357,7 +11407,7 @@
         </is>
       </c>
     </row>
-    <row r="322">
+    <row r="322" ht="28" customHeight="1">
       <c r="A322" s="2" t="n">
         <v>321</v>
       </c>
@@ -11391,7 +11441,7 @@
         </is>
       </c>
     </row>
-    <row r="323">
+    <row r="323" ht="28" customHeight="1">
       <c r="A323" s="2" t="n">
         <v>322</v>
       </c>
@@ -11425,7 +11475,7 @@
         </is>
       </c>
     </row>
-    <row r="324">
+    <row r="324" ht="28" customHeight="1">
       <c r="A324" s="2" t="n">
         <v>323</v>
       </c>
@@ -11459,7 +11509,7 @@
         </is>
       </c>
     </row>
-    <row r="325">
+    <row r="325" ht="28" customHeight="1">
       <c r="A325" s="2" t="n">
         <v>324</v>
       </c>
@@ -11493,7 +11543,7 @@
         </is>
       </c>
     </row>
-    <row r="326">
+    <row r="326" ht="28" customHeight="1">
       <c r="A326" s="2" t="n">
         <v>325</v>
       </c>
@@ -11527,7 +11577,7 @@
         </is>
       </c>
     </row>
-    <row r="327">
+    <row r="327" ht="28" customHeight="1">
       <c r="A327" s="2" t="n">
         <v>326</v>
       </c>
@@ -11561,7 +11611,7 @@
         </is>
       </c>
     </row>
-    <row r="328">
+    <row r="328" ht="28" customHeight="1">
       <c r="A328" s="2" t="n">
         <v>327</v>
       </c>
@@ -11595,7 +11645,7 @@
         </is>
       </c>
     </row>
-    <row r="329">
+    <row r="329" ht="28" customHeight="1">
       <c r="A329" s="2" t="n">
         <v>328</v>
       </c>
@@ -11629,7 +11679,7 @@
         </is>
       </c>
     </row>
-    <row r="330">
+    <row r="330" ht="28" customHeight="1">
       <c r="A330" s="2" t="n">
         <v>329</v>
       </c>
@@ -11663,7 +11713,7 @@
         </is>
       </c>
     </row>
-    <row r="331">
+    <row r="331" ht="28" customHeight="1">
       <c r="A331" s="2" t="n">
         <v>330</v>
       </c>
@@ -11697,7 +11747,7 @@
         </is>
       </c>
     </row>
-    <row r="332">
+    <row r="332" ht="28" customHeight="1">
       <c r="A332" s="2" t="n">
         <v>331</v>
       </c>
@@ -11731,7 +11781,7 @@
         </is>
       </c>
     </row>
-    <row r="333">
+    <row r="333" ht="28" customHeight="1">
       <c r="A333" s="2" t="n">
         <v>332</v>
       </c>
@@ -11765,7 +11815,7 @@
         </is>
       </c>
     </row>
-    <row r="334">
+    <row r="334" ht="28" customHeight="1">
       <c r="A334" s="2" t="n">
         <v>333</v>
       </c>
@@ -11799,7 +11849,7 @@
         </is>
       </c>
     </row>
-    <row r="335">
+    <row r="335" ht="28" customHeight="1">
       <c r="A335" s="2" t="n">
         <v>334</v>
       </c>
@@ -11833,7 +11883,7 @@
         </is>
       </c>
     </row>
-    <row r="336">
+    <row r="336" ht="28" customHeight="1">
       <c r="A336" s="2" t="n">
         <v>335</v>
       </c>
@@ -11867,7 +11917,7 @@
         </is>
       </c>
     </row>
-    <row r="337">
+    <row r="337" ht="28" customHeight="1">
       <c r="A337" s="2" t="n">
         <v>336</v>
       </c>
@@ -11901,7 +11951,7 @@
         </is>
       </c>
     </row>
-    <row r="338">
+    <row r="338" ht="28" customHeight="1">
       <c r="A338" s="2" t="n">
         <v>337</v>
       </c>
@@ -11935,7 +11985,7 @@
         </is>
       </c>
     </row>
-    <row r="339">
+    <row r="339" ht="28" customHeight="1">
       <c r="A339" s="2" t="n">
         <v>338</v>
       </c>
@@ -11969,7 +12019,7 @@
         </is>
       </c>
     </row>
-    <row r="340">
+    <row r="340" ht="28" customHeight="1">
       <c r="A340" s="2" t="n">
         <v>339</v>
       </c>
@@ -12003,7 +12053,7 @@
         </is>
       </c>
     </row>
-    <row r="341">
+    <row r="341" ht="28" customHeight="1">
       <c r="A341" s="2" t="n">
         <v>340</v>
       </c>
@@ -12037,7 +12087,7 @@
         </is>
       </c>
     </row>
-    <row r="342">
+    <row r="342" ht="28" customHeight="1">
       <c r="A342" s="2" t="n">
         <v>341</v>
       </c>
@@ -12071,7 +12121,7 @@
         </is>
       </c>
     </row>
-    <row r="343">
+    <row r="343" ht="28" customHeight="1">
       <c r="A343" s="2" t="n">
         <v>342</v>
       </c>
@@ -12105,7 +12155,7 @@
         </is>
       </c>
     </row>
-    <row r="344">
+    <row r="344" ht="28" customHeight="1">
       <c r="A344" s="2" t="n">
         <v>343</v>
       </c>
@@ -12139,7 +12189,7 @@
         </is>
       </c>
     </row>
-    <row r="345">
+    <row r="345" ht="28" customHeight="1">
       <c r="A345" s="2" t="n">
         <v>344</v>
       </c>
@@ -12173,7 +12223,7 @@
         </is>
       </c>
     </row>
-    <row r="346">
+    <row r="346" ht="28" customHeight="1">
       <c r="A346" s="2" t="n">
         <v>345</v>
       </c>
@@ -12207,7 +12257,7 @@
         </is>
       </c>
     </row>
-    <row r="347">
+    <row r="347" ht="28" customHeight="1">
       <c r="A347" s="2" t="n">
         <v>346</v>
       </c>
@@ -12241,7 +12291,7 @@
         </is>
       </c>
     </row>
-    <row r="348">
+    <row r="348" ht="28" customHeight="1">
       <c r="A348" s="2" t="n">
         <v>347</v>
       </c>
@@ -12275,7 +12325,7 @@
         </is>
       </c>
     </row>
-    <row r="349">
+    <row r="349" ht="28" customHeight="1">
       <c r="A349" s="2" t="n">
         <v>348</v>
       </c>
@@ -12309,7 +12359,7 @@
         </is>
       </c>
     </row>
-    <row r="350">
+    <row r="350" ht="28" customHeight="1">
       <c r="A350" s="2" t="n">
         <v>349</v>
       </c>
@@ -12343,7 +12393,7 @@
         </is>
       </c>
     </row>
-    <row r="351">
+    <row r="351" ht="28" customHeight="1">
       <c r="A351" s="2" t="n">
         <v>350</v>
       </c>
@@ -12377,7 +12427,7 @@
         </is>
       </c>
     </row>
-    <row r="352">
+    <row r="352" ht="28" customHeight="1">
       <c r="A352" s="2" t="n">
         <v>351</v>
       </c>
@@ -12411,7 +12461,7 @@
         </is>
       </c>
     </row>
-    <row r="353">
+    <row r="353" ht="28" customHeight="1">
       <c r="A353" s="2" t="n">
         <v>352</v>
       </c>
@@ -12445,7 +12495,7 @@
         </is>
       </c>
     </row>
-    <row r="354">
+    <row r="354" ht="28" customHeight="1">
       <c r="A354" s="2" t="n">
         <v>353</v>
       </c>
@@ -12479,7 +12529,7 @@
         </is>
       </c>
     </row>
-    <row r="355">
+    <row r="355" ht="28" customHeight="1">
       <c r="A355" s="2" t="n">
         <v>354</v>
       </c>
@@ -12513,7 +12563,7 @@
         </is>
       </c>
     </row>
-    <row r="356">
+    <row r="356" ht="28" customHeight="1">
       <c r="A356" s="2" t="n">
         <v>355</v>
       </c>
@@ -12547,7 +12597,7 @@
         </is>
       </c>
     </row>
-    <row r="357">
+    <row r="357" ht="28" customHeight="1">
       <c r="A357" s="2" t="n">
         <v>356</v>
       </c>
@@ -12581,7 +12631,7 @@
         </is>
       </c>
     </row>
-    <row r="358">
+    <row r="358" ht="28" customHeight="1">
       <c r="A358" s="2" t="n">
         <v>357</v>
       </c>
@@ -12615,7 +12665,7 @@
         </is>
       </c>
     </row>
-    <row r="359">
+    <row r="359" ht="28" customHeight="1">
       <c r="A359" s="2" t="n">
         <v>358</v>
       </c>
@@ -12649,7 +12699,7 @@
         </is>
       </c>
     </row>
-    <row r="360">
+    <row r="360" ht="28" customHeight="1">
       <c r="A360" s="2" t="n">
         <v>359</v>
       </c>
@@ -12683,7 +12733,7 @@
         </is>
       </c>
     </row>
-    <row r="361">
+    <row r="361" ht="28" customHeight="1">
       <c r="A361" s="2" t="n">
         <v>360</v>
       </c>
@@ -12717,7 +12767,7 @@
         </is>
       </c>
     </row>
-    <row r="362">
+    <row r="362" ht="28" customHeight="1">
       <c r="A362" s="2" t="n">
         <v>361</v>
       </c>
@@ -12751,7 +12801,7 @@
         </is>
       </c>
     </row>
-    <row r="363">
+    <row r="363" ht="28" customHeight="1">
       <c r="A363" s="2" t="n">
         <v>362</v>
       </c>
@@ -12785,7 +12835,7 @@
         </is>
       </c>
     </row>
-    <row r="364">
+    <row r="364" ht="28" customHeight="1">
       <c r="A364" s="2" t="n">
         <v>363</v>
       </c>
@@ -12819,7 +12869,7 @@
         </is>
       </c>
     </row>
-    <row r="365">
+    <row r="365" ht="28" customHeight="1">
       <c r="A365" s="2" t="n">
         <v>364</v>
       </c>
@@ -12853,7 +12903,7 @@
         </is>
       </c>
     </row>
-    <row r="366">
+    <row r="366" ht="28" customHeight="1">
       <c r="A366" s="2" t="n">
         <v>365</v>
       </c>
@@ -12887,7 +12937,7 @@
         </is>
       </c>
     </row>
-    <row r="367">
+    <row r="367" ht="28" customHeight="1">
       <c r="A367" s="2" t="n">
         <v>366</v>
       </c>
@@ -12921,7 +12971,7 @@
         </is>
       </c>
     </row>
-    <row r="368">
+    <row r="368" ht="28" customHeight="1">
       <c r="A368" s="2" t="n">
         <v>367</v>
       </c>
@@ -12955,7 +13005,7 @@
         </is>
       </c>
     </row>
-    <row r="369">
+    <row r="369" ht="28" customHeight="1">
       <c r="A369" s="2" t="n">
         <v>368</v>
       </c>
@@ -12989,7 +13039,7 @@
         </is>
       </c>
     </row>
-    <row r="370">
+    <row r="370" ht="28" customHeight="1">
       <c r="A370" s="2" t="n">
         <v>369</v>
       </c>
@@ -13023,7 +13073,7 @@
         </is>
       </c>
     </row>
-    <row r="371">
+    <row r="371" ht="28" customHeight="1">
       <c r="A371" s="2" t="n">
         <v>370</v>
       </c>
@@ -13057,7 +13107,7 @@
         </is>
       </c>
     </row>
-    <row r="372">
+    <row r="372" ht="28" customHeight="1">
       <c r="A372" s="2" t="n">
         <v>371</v>
       </c>
@@ -13091,7 +13141,7 @@
         </is>
       </c>
     </row>
-    <row r="373">
+    <row r="373" ht="28" customHeight="1">
       <c r="A373" s="2" t="n">
         <v>372</v>
       </c>
@@ -13125,7 +13175,7 @@
         </is>
       </c>
     </row>
-    <row r="374">
+    <row r="374" ht="28" customHeight="1">
       <c r="A374" s="2" t="n">
         <v>373</v>
       </c>
@@ -13159,7 +13209,7 @@
         </is>
       </c>
     </row>
-    <row r="375">
+    <row r="375" ht="28" customHeight="1">
       <c r="A375" s="2" t="n">
         <v>374</v>
       </c>
@@ -13193,7 +13243,7 @@
         </is>
       </c>
     </row>
-    <row r="376">
+    <row r="376" ht="28" customHeight="1">
       <c r="A376" s="2" t="n">
         <v>375</v>
       </c>
@@ -13227,7 +13277,7 @@
         </is>
       </c>
     </row>
-    <row r="377">
+    <row r="377" ht="28" customHeight="1">
       <c r="A377" s="2" t="n">
         <v>376</v>
       </c>
@@ -13261,7 +13311,7 @@
         </is>
       </c>
     </row>
-    <row r="378">
+    <row r="378" ht="28" customHeight="1">
       <c r="A378" s="2" t="n">
         <v>377</v>
       </c>
@@ -13295,7 +13345,7 @@
         </is>
       </c>
     </row>
-    <row r="379">
+    <row r="379" ht="28" customHeight="1">
       <c r="A379" s="2" t="n">
         <v>378</v>
       </c>
@@ -13329,7 +13379,7 @@
         </is>
       </c>
     </row>
-    <row r="380">
+    <row r="380" ht="28" customHeight="1">
       <c r="A380" s="2" t="n">
         <v>379</v>
       </c>
@@ -13363,7 +13413,7 @@
         </is>
       </c>
     </row>
-    <row r="381">
+    <row r="381" ht="28" customHeight="1">
       <c r="A381" s="2" t="n">
         <v>380</v>
       </c>
@@ -13397,7 +13447,7 @@
         </is>
       </c>
     </row>
-    <row r="382">
+    <row r="382" ht="28" customHeight="1">
       <c r="A382" s="2" t="n">
         <v>381</v>
       </c>
@@ -13431,7 +13481,7 @@
         </is>
       </c>
     </row>
-    <row r="383">
+    <row r="383" ht="28" customHeight="1">
       <c r="A383" s="2" t="n">
         <v>382</v>
       </c>
@@ -13465,7 +13515,7 @@
         </is>
       </c>
     </row>
-    <row r="384">
+    <row r="384" ht="28" customHeight="1">
       <c r="A384" s="2" t="n">
         <v>383</v>
       </c>
@@ -13499,7 +13549,7 @@
         </is>
       </c>
     </row>
-    <row r="385">
+    <row r="385" ht="28" customHeight="1">
       <c r="A385" s="2" t="n">
         <v>384</v>
       </c>
@@ -13533,7 +13583,7 @@
         </is>
       </c>
     </row>
-    <row r="386">
+    <row r="386" ht="28" customHeight="1">
       <c r="A386" s="2" t="n">
         <v>385</v>
       </c>
@@ -13567,7 +13617,7 @@
         </is>
       </c>
     </row>
-    <row r="387">
+    <row r="387" ht="28" customHeight="1">
       <c r="A387" s="2" t="n">
         <v>386</v>
       </c>
@@ -13601,7 +13651,7 @@
         </is>
       </c>
     </row>
-    <row r="388">
+    <row r="388" ht="28" customHeight="1">
       <c r="A388" s="2" t="n">
         <v>387</v>
       </c>
@@ -13635,7 +13685,7 @@
         </is>
       </c>
     </row>
-    <row r="389">
+    <row r="389" ht="28" customHeight="1">
       <c r="A389" s="2" t="n">
         <v>388</v>
       </c>
@@ -13669,7 +13719,7 @@
         </is>
       </c>
     </row>
-    <row r="390">
+    <row r="390" ht="28" customHeight="1">
       <c r="A390" s="2" t="n">
         <v>389</v>
       </c>
@@ -13703,7 +13753,7 @@
         </is>
       </c>
     </row>
-    <row r="391">
+    <row r="391" ht="28" customHeight="1">
       <c r="A391" s="2" t="n">
         <v>390</v>
       </c>
@@ -13737,7 +13787,7 @@
         </is>
       </c>
     </row>
-    <row r="392">
+    <row r="392" ht="28" customHeight="1">
       <c r="A392" s="2" t="n">
         <v>391</v>
       </c>
@@ -13771,7 +13821,7 @@
         </is>
       </c>
     </row>
-    <row r="393">
+    <row r="393" ht="28" customHeight="1">
       <c r="A393" s="2" t="n">
         <v>392</v>
       </c>
@@ -13805,7 +13855,7 @@
         </is>
       </c>
     </row>
-    <row r="394">
+    <row r="394" ht="28" customHeight="1">
       <c r="A394" s="2" t="n">
         <v>393</v>
       </c>
@@ -13839,7 +13889,7 @@
         </is>
       </c>
     </row>
-    <row r="395">
+    <row r="395" ht="28" customHeight="1">
       <c r="A395" s="2" t="n">
         <v>394</v>
       </c>
@@ -13873,7 +13923,7 @@
         </is>
       </c>
     </row>
-    <row r="396">
+    <row r="396" ht="28" customHeight="1">
       <c r="A396" s="2" t="n">
         <v>395</v>
       </c>
@@ -13907,7 +13957,7 @@
         </is>
       </c>
     </row>
-    <row r="397">
+    <row r="397" ht="28" customHeight="1">
       <c r="A397" s="2" t="n">
         <v>396</v>
       </c>
@@ -13941,7 +13991,7 @@
         </is>
       </c>
     </row>
-    <row r="398">
+    <row r="398" ht="28" customHeight="1">
       <c r="A398" s="2" t="n">
         <v>397</v>
       </c>
@@ -13975,7 +14025,7 @@
         </is>
       </c>
     </row>
-    <row r="399">
+    <row r="399" ht="28" customHeight="1">
       <c r="A399" s="2" t="n">
         <v>398</v>
       </c>
@@ -14009,7 +14059,7 @@
         </is>
       </c>
     </row>
-    <row r="400">
+    <row r="400" ht="28" customHeight="1">
       <c r="A400" s="2" t="n">
         <v>399</v>
       </c>
@@ -14043,7 +14093,7 @@
         </is>
       </c>
     </row>
-    <row r="401">
+    <row r="401" ht="28" customHeight="1">
       <c r="A401" s="2" t="n">
         <v>400</v>
       </c>
@@ -14077,7 +14127,7 @@
         </is>
       </c>
     </row>
-    <row r="402">
+    <row r="402" ht="28" customHeight="1">
       <c r="A402" s="2" t="n">
         <v>401</v>
       </c>
@@ -14111,7 +14161,7 @@
         </is>
       </c>
     </row>
-    <row r="403">
+    <row r="403" ht="28" customHeight="1">
       <c r="A403" s="2" t="n">
         <v>402</v>
       </c>
@@ -14145,7 +14195,7 @@
         </is>
       </c>
     </row>
-    <row r="404">
+    <row r="404" ht="28" customHeight="1">
       <c r="A404" s="2" t="n">
         <v>403</v>
       </c>
@@ -14179,7 +14229,7 @@
         </is>
       </c>
     </row>
-    <row r="405">
+    <row r="405" ht="28" customHeight="1">
       <c r="A405" s="2" t="n">
         <v>404</v>
       </c>
@@ -14213,7 +14263,7 @@
         </is>
       </c>
     </row>
-    <row r="406">
+    <row r="406" ht="28" customHeight="1">
       <c r="A406" s="2" t="n">
         <v>405</v>
       </c>
@@ -14247,7 +14297,7 @@
         </is>
       </c>
     </row>
-    <row r="407">
+    <row r="407" ht="28" customHeight="1">
       <c r="A407" s="2" t="n">
         <v>406</v>
       </c>
@@ -14281,7 +14331,7 @@
         </is>
       </c>
     </row>
-    <row r="408">
+    <row r="408" ht="28" customHeight="1">
       <c r="A408" s="2" t="n">
         <v>407</v>
       </c>
@@ -14315,7 +14365,7 @@
         </is>
       </c>
     </row>
-    <row r="409">
+    <row r="409" ht="28" customHeight="1">
       <c r="A409" s="2" t="n">
         <v>408</v>
       </c>
@@ -14349,7 +14399,7 @@
         </is>
       </c>
     </row>
-    <row r="410">
+    <row r="410" ht="28" customHeight="1">
       <c r="A410" s="2" t="n">
         <v>409</v>
       </c>
@@ -14383,7 +14433,7 @@
         </is>
       </c>
     </row>
-    <row r="411">
+    <row r="411" ht="28" customHeight="1">
       <c r="A411" s="2" t="n">
         <v>410</v>
       </c>
@@ -14417,7 +14467,7 @@
         </is>
       </c>
     </row>
-    <row r="412">
+    <row r="412" ht="28" customHeight="1">
       <c r="A412" s="2" t="n">
         <v>411</v>
       </c>
@@ -14451,7 +14501,7 @@
         </is>
       </c>
     </row>
-    <row r="413">
+    <row r="413" ht="28" customHeight="1">
       <c r="A413" s="2" t="n">
         <v>412</v>
       </c>
@@ -14485,7 +14535,7 @@
         </is>
       </c>
     </row>
-    <row r="414">
+    <row r="414" ht="28" customHeight="1">
       <c r="A414" s="2" t="n">
         <v>413</v>
       </c>
@@ -14519,7 +14569,7 @@
         </is>
       </c>
     </row>
-    <row r="415">
+    <row r="415" ht="28" customHeight="1">
       <c r="A415" s="2" t="n">
         <v>414</v>
       </c>
@@ -14553,7 +14603,7 @@
         </is>
       </c>
     </row>
-    <row r="416">
+    <row r="416" ht="28" customHeight="1">
       <c r="A416" s="2" t="n">
         <v>415</v>
       </c>
@@ -14587,7 +14637,7 @@
         </is>
       </c>
     </row>
-    <row r="417">
+    <row r="417" ht="28" customHeight="1">
       <c r="A417" s="2" t="n">
         <v>416</v>
       </c>
@@ -14621,7 +14671,7 @@
         </is>
       </c>
     </row>
-    <row r="418">
+    <row r="418" ht="28" customHeight="1">
       <c r="A418" s="2" t="n">
         <v>417</v>
       </c>
@@ -14655,7 +14705,7 @@
         </is>
       </c>
     </row>
-    <row r="419">
+    <row r="419" ht="28" customHeight="1">
       <c r="A419" s="2" t="n">
         <v>418</v>
       </c>
@@ -14689,7 +14739,7 @@
         </is>
       </c>
     </row>
-    <row r="420">
+    <row r="420" ht="28" customHeight="1">
       <c r="A420" s="2" t="n">
         <v>419</v>
       </c>
@@ -14723,7 +14773,7 @@
         </is>
       </c>
     </row>
-    <row r="421">
+    <row r="421" ht="28" customHeight="1">
       <c r="A421" s="2" t="n">
         <v>420</v>
       </c>
@@ -14757,7 +14807,7 @@
         </is>
       </c>
     </row>
-    <row r="422">
+    <row r="422" ht="28" customHeight="1">
       <c r="A422" s="2" t="n">
         <v>421</v>
       </c>
@@ -14791,7 +14841,7 @@
         </is>
       </c>
     </row>
-    <row r="423">
+    <row r="423" ht="28" customHeight="1">
       <c r="A423" s="2" t="n">
         <v>422</v>
       </c>
@@ -14825,7 +14875,7 @@
         </is>
       </c>
     </row>
-    <row r="424">
+    <row r="424" ht="28" customHeight="1">
       <c r="A424" s="2" t="n">
         <v>423</v>
       </c>
@@ -14859,7 +14909,7 @@
         </is>
       </c>
     </row>
-    <row r="425">
+    <row r="425" ht="28" customHeight="1">
       <c r="A425" s="2" t="n">
         <v>424</v>
       </c>
@@ -14893,7 +14943,7 @@
         </is>
       </c>
     </row>
-    <row r="426">
+    <row r="426" ht="28" customHeight="1">
       <c r="A426" s="2" t="n">
         <v>425</v>
       </c>
@@ -14927,7 +14977,7 @@
         </is>
       </c>
     </row>
-    <row r="427">
+    <row r="427" ht="28" customHeight="1">
       <c r="A427" s="2" t="n">
         <v>426</v>
       </c>
@@ -14961,7 +15011,7 @@
         </is>
       </c>
     </row>
-    <row r="428">
+    <row r="428" ht="28" customHeight="1">
       <c r="A428" s="2" t="n">
         <v>427</v>
       </c>
@@ -14995,7 +15045,7 @@
         </is>
       </c>
     </row>
-    <row r="429">
+    <row r="429" ht="28" customHeight="1">
       <c r="A429" s="2" t="n">
         <v>428</v>
       </c>
@@ -15029,7 +15079,7 @@
         </is>
       </c>
     </row>
-    <row r="430">
+    <row r="430" ht="28" customHeight="1">
       <c r="A430" s="2" t="n">
         <v>429</v>
       </c>
@@ -15063,7 +15113,7 @@
         </is>
       </c>
     </row>
-    <row r="431">
+    <row r="431" ht="28" customHeight="1">
       <c r="A431" s="2" t="n">
         <v>430</v>
       </c>
@@ -15097,7 +15147,7 @@
         </is>
       </c>
     </row>
-    <row r="432">
+    <row r="432" ht="28" customHeight="1">
       <c r="A432" s="2" t="n">
         <v>431</v>
       </c>
@@ -15131,7 +15181,7 @@
         </is>
       </c>
     </row>
-    <row r="433">
+    <row r="433" ht="28" customHeight="1">
       <c r="A433" s="2" t="n">
         <v>432</v>
       </c>
@@ -15165,7 +15215,7 @@
         </is>
       </c>
     </row>
-    <row r="434">
+    <row r="434" ht="28" customHeight="1">
       <c r="A434" s="2" t="n">
         <v>433</v>
       </c>
@@ -15199,7 +15249,7 @@
         </is>
       </c>
     </row>
-    <row r="435">
+    <row r="435" ht="28" customHeight="1">
       <c r="A435" s="2" t="n">
         <v>434</v>
       </c>
@@ -15233,7 +15283,7 @@
         </is>
       </c>
     </row>
-    <row r="436">
+    <row r="436" ht="28" customHeight="1">
       <c r="A436" s="2" t="n">
         <v>435</v>
       </c>
@@ -15267,7 +15317,7 @@
         </is>
       </c>
     </row>
-    <row r="437">
+    <row r="437" ht="28" customHeight="1">
       <c r="A437" s="2" t="n">
         <v>436</v>
       </c>
@@ -15301,7 +15351,7 @@
         </is>
       </c>
     </row>
-    <row r="438">
+    <row r="438" ht="28" customHeight="1">
       <c r="A438" s="2" t="n">
         <v>437</v>
       </c>
@@ -15335,7 +15385,7 @@
         </is>
       </c>
     </row>
-    <row r="439">
+    <row r="439" ht="28" customHeight="1">
       <c r="A439" s="2" t="n">
         <v>438</v>
       </c>
@@ -15369,7 +15419,7 @@
         </is>
       </c>
     </row>
-    <row r="440">
+    <row r="440" ht="28" customHeight="1">
       <c r="A440" s="2" t="n">
         <v>439</v>
       </c>
@@ -15403,7 +15453,7 @@
         </is>
       </c>
     </row>
-    <row r="441">
+    <row r="441" ht="28" customHeight="1">
       <c r="A441" s="2" t="n">
         <v>440</v>
       </c>
@@ -15437,7 +15487,7 @@
         </is>
       </c>
     </row>
-    <row r="442">
+    <row r="442" ht="28" customHeight="1">
       <c r="A442" s="2" t="n">
         <v>441</v>
       </c>
@@ -15471,7 +15521,7 @@
         </is>
       </c>
     </row>
-    <row r="443">
+    <row r="443" ht="28" customHeight="1">
       <c r="A443" s="2" t="n">
         <v>442</v>
       </c>
@@ -15505,7 +15555,7 @@
         </is>
       </c>
     </row>
-    <row r="444">
+    <row r="444" ht="28" customHeight="1">
       <c r="A444" s="2" t="n">
         <v>443</v>
       </c>
@@ -15539,7 +15589,7 @@
         </is>
       </c>
     </row>
-    <row r="445">
+    <row r="445" ht="28" customHeight="1">
       <c r="A445" s="2" t="n">
         <v>444</v>
       </c>
@@ -15573,7 +15623,7 @@
         </is>
       </c>
     </row>
-    <row r="446">
+    <row r="446" ht="28" customHeight="1">
       <c r="A446" s="2" t="n">
         <v>445</v>
       </c>
@@ -15607,7 +15657,7 @@
         </is>
       </c>
     </row>
-    <row r="447">
+    <row r="447" ht="28" customHeight="1">
       <c r="A447" s="2" t="n">
         <v>446</v>
       </c>
@@ -15641,7 +15691,7 @@
         </is>
       </c>
     </row>
-    <row r="448">
+    <row r="448" ht="28" customHeight="1">
       <c r="A448" s="2" t="n">
         <v>447</v>
       </c>
@@ -15675,7 +15725,7 @@
         </is>
       </c>
     </row>
-    <row r="449">
+    <row r="449" ht="28" customHeight="1">
       <c r="A449" s="2" t="n">
         <v>448</v>
       </c>
@@ -15709,7 +15759,7 @@
         </is>
       </c>
     </row>
-    <row r="450">
+    <row r="450" ht="28" customHeight="1">
       <c r="A450" s="2" t="n">
         <v>449</v>
       </c>
@@ -15743,7 +15793,7 @@
         </is>
       </c>
     </row>
-    <row r="451">
+    <row r="451" ht="28" customHeight="1">
       <c r="A451" s="2" t="n">
         <v>450</v>
       </c>
@@ -15777,7 +15827,7 @@
         </is>
       </c>
     </row>
-    <row r="452">
+    <row r="452" ht="28" customHeight="1">
       <c r="A452" s="2" t="n">
         <v>451</v>
       </c>
@@ -15811,7 +15861,7 @@
         </is>
       </c>
     </row>
-    <row r="453">
+    <row r="453" ht="28" customHeight="1">
       <c r="A453" s="2" t="n">
         <v>452</v>
       </c>
@@ -15845,7 +15895,7 @@
         </is>
       </c>
     </row>
-    <row r="454">
+    <row r="454" ht="28" customHeight="1">
       <c r="A454" s="2" t="n">
         <v>453</v>
       </c>
@@ -15879,7 +15929,7 @@
         </is>
       </c>
     </row>
-    <row r="455">
+    <row r="455" ht="28" customHeight="1">
       <c r="A455" s="2" t="n">
         <v>454</v>
       </c>
@@ -15913,7 +15963,7 @@
         </is>
       </c>
     </row>
-    <row r="456">
+    <row r="456" ht="28" customHeight="1">
       <c r="A456" s="2" t="n">
         <v>455</v>
       </c>
@@ -15947,7 +15997,7 @@
         </is>
       </c>
     </row>
-    <row r="457">
+    <row r="457" ht="28" customHeight="1">
       <c r="A457" s="2" t="n">
         <v>456</v>
       </c>
@@ -15981,7 +16031,7 @@
         </is>
       </c>
     </row>
-    <row r="458">
+    <row r="458" ht="28" customHeight="1">
       <c r="A458" s="2" t="n">
         <v>457</v>
       </c>
@@ -16015,7 +16065,7 @@
         </is>
       </c>
     </row>
-    <row r="459">
+    <row r="459" ht="28" customHeight="1">
       <c r="A459" s="2" t="n">
         <v>458</v>
       </c>
@@ -16049,7 +16099,7 @@
         </is>
       </c>
     </row>
-    <row r="460">
+    <row r="460" ht="28" customHeight="1">
       <c r="A460" s="2" t="n">
         <v>459</v>
       </c>
@@ -16083,7 +16133,7 @@
         </is>
       </c>
     </row>
-    <row r="461">
+    <row r="461" ht="28" customHeight="1">
       <c r="A461" s="2" t="n">
         <v>460</v>
       </c>
@@ -16117,7 +16167,7 @@
         </is>
       </c>
     </row>
-    <row r="462">
+    <row r="462" ht="28" customHeight="1">
       <c r="A462" s="2" t="n">
         <v>461</v>
       </c>
@@ -16151,7 +16201,7 @@
         </is>
       </c>
     </row>
-    <row r="463">
+    <row r="463" ht="28" customHeight="1">
       <c r="A463" s="2" t="n">
         <v>462</v>
       </c>
@@ -16185,7 +16235,7 @@
         </is>
       </c>
     </row>
-    <row r="464">
+    <row r="464" ht="28" customHeight="1">
       <c r="A464" s="2" t="n">
         <v>463</v>
       </c>
@@ -16219,7 +16269,7 @@
         </is>
       </c>
     </row>
-    <row r="465">
+    <row r="465" ht="28" customHeight="1">
       <c r="A465" s="2" t="n">
         <v>464</v>
       </c>
@@ -16253,7 +16303,7 @@
         </is>
       </c>
     </row>
-    <row r="466">
+    <row r="466" ht="28" customHeight="1">
       <c r="A466" s="2" t="n">
         <v>465</v>
       </c>
@@ -16287,7 +16337,7 @@
         </is>
       </c>
     </row>
-    <row r="467">
+    <row r="467" ht="28" customHeight="1">
       <c r="A467" s="2" t="n">
         <v>466</v>
       </c>
@@ -16321,7 +16371,7 @@
         </is>
       </c>
     </row>
-    <row r="468">
+    <row r="468" ht="28" customHeight="1">
       <c r="A468" s="2" t="n">
         <v>467</v>
       </c>
@@ -16355,7 +16405,7 @@
         </is>
       </c>
     </row>
-    <row r="469">
+    <row r="469" ht="28" customHeight="1">
       <c r="A469" s="2" t="n">
         <v>468</v>
       </c>
@@ -16389,7 +16439,7 @@
         </is>
       </c>
     </row>
-    <row r="470">
+    <row r="470" ht="28" customHeight="1">
       <c r="A470" s="2" t="n">
         <v>469</v>
       </c>
@@ -16423,7 +16473,7 @@
         </is>
       </c>
     </row>
-    <row r="471">
+    <row r="471" ht="28" customHeight="1">
       <c r="A471" s="2" t="n">
         <v>470</v>
       </c>
@@ -16457,7 +16507,7 @@
         </is>
       </c>
     </row>
-    <row r="472">
+    <row r="472" ht="28" customHeight="1">
       <c r="A472" s="2" t="n">
         <v>471</v>
       </c>
@@ -16491,7 +16541,7 @@
         </is>
       </c>
     </row>
-    <row r="473">
+    <row r="473" ht="28" customHeight="1">
       <c r="A473" s="2" t="n">
         <v>472</v>
       </c>
@@ -16525,7 +16575,7 @@
         </is>
       </c>
     </row>
-    <row r="474">
+    <row r="474" ht="28" customHeight="1">
       <c r="A474" s="2" t="n">
         <v>473</v>
       </c>
@@ -16559,7 +16609,7 @@
         </is>
       </c>
     </row>
-    <row r="475">
+    <row r="475" ht="28" customHeight="1">
       <c r="A475" s="2" t="n">
         <v>474</v>
       </c>
@@ -16593,7 +16643,7 @@
         </is>
       </c>
     </row>
-    <row r="476">
+    <row r="476" ht="28" customHeight="1">
       <c r="A476" s="2" t="n">
         <v>475</v>
       </c>
@@ -16627,7 +16677,7 @@
         </is>
       </c>
     </row>
-    <row r="477">
+    <row r="477" ht="28" customHeight="1">
       <c r="A477" s="2" t="n">
         <v>476</v>
       </c>
@@ -16661,7 +16711,7 @@
         </is>
       </c>
     </row>
-    <row r="478">
+    <row r="478" ht="28" customHeight="1">
       <c r="A478" s="2" t="n">
         <v>477</v>
       </c>
@@ -16695,7 +16745,7 @@
         </is>
       </c>
     </row>
-    <row r="479">
+    <row r="479" ht="28" customHeight="1">
       <c r="A479" s="2" t="n">
         <v>478</v>
       </c>
@@ -16729,7 +16779,7 @@
         </is>
       </c>
     </row>
-    <row r="480">
+    <row r="480" ht="28" customHeight="1">
       <c r="A480" s="2" t="n">
         <v>479</v>
       </c>
@@ -16763,7 +16813,7 @@
         </is>
       </c>
     </row>
-    <row r="481">
+    <row r="481" ht="28" customHeight="1">
       <c r="A481" s="2" t="n">
         <v>480</v>
       </c>
@@ -16797,7 +16847,7 @@
         </is>
       </c>
     </row>
-    <row r="482">
+    <row r="482" ht="28" customHeight="1">
       <c r="A482" s="2" t="n">
         <v>481</v>
       </c>
@@ -16831,7 +16881,7 @@
         </is>
       </c>
     </row>
-    <row r="483">
+    <row r="483" ht="28" customHeight="1">
       <c r="A483" s="2" t="n">
         <v>482</v>
       </c>
@@ -16865,7 +16915,7 @@
         </is>
       </c>
     </row>
-    <row r="484">
+    <row r="484" ht="28" customHeight="1">
       <c r="A484" s="2" t="n">
         <v>483</v>
       </c>
@@ -16899,7 +16949,7 @@
         </is>
       </c>
     </row>
-    <row r="485">
+    <row r="485" ht="28" customHeight="1">
       <c r="A485" s="2" t="n">
         <v>484</v>
       </c>
@@ -16933,7 +16983,7 @@
         </is>
       </c>
     </row>
-    <row r="486">
+    <row r="486" ht="28" customHeight="1">
       <c r="A486" s="2" t="n">
         <v>485</v>
       </c>
@@ -16967,7 +17017,7 @@
         </is>
       </c>
     </row>
-    <row r="487">
+    <row r="487" ht="28" customHeight="1">
       <c r="A487" s="2" t="n">
         <v>486</v>
       </c>
@@ -17001,7 +17051,7 @@
         </is>
       </c>
     </row>
-    <row r="488">
+    <row r="488" ht="28" customHeight="1">
       <c r="A488" s="2" t="n">
         <v>487</v>
       </c>
@@ -17035,7 +17085,7 @@
         </is>
       </c>
     </row>
-    <row r="489">
+    <row r="489" ht="28" customHeight="1">
       <c r="A489" s="2" t="n">
         <v>488</v>
       </c>
@@ -17069,7 +17119,7 @@
         </is>
       </c>
     </row>
-    <row r="490">
+    <row r="490" ht="28" customHeight="1">
       <c r="A490" s="2" t="n">
         <v>489</v>
       </c>
@@ -17103,7 +17153,7 @@
         </is>
       </c>
     </row>
-    <row r="491">
+    <row r="491" ht="28" customHeight="1">
       <c r="A491" s="2" t="n">
         <v>490</v>
       </c>
@@ -17137,7 +17187,7 @@
         </is>
       </c>
     </row>
-    <row r="492">
+    <row r="492" ht="28" customHeight="1">
       <c r="A492" s="2" t="n">
         <v>491</v>
       </c>
@@ -17171,7 +17221,7 @@
         </is>
       </c>
     </row>
-    <row r="493">
+    <row r="493" ht="28" customHeight="1">
       <c r="A493" s="2" t="n">
         <v>492</v>
       </c>
@@ -17205,7 +17255,7 @@
         </is>
       </c>
     </row>
-    <row r="494">
+    <row r="494" ht="28" customHeight="1">
       <c r="A494" s="2" t="n">
         <v>493</v>
       </c>
@@ -17239,7 +17289,7 @@
         </is>
       </c>
     </row>
-    <row r="495">
+    <row r="495" ht="28" customHeight="1">
       <c r="A495" s="2" t="n">
         <v>494</v>
       </c>
@@ -17273,7 +17323,7 @@
         </is>
       </c>
     </row>
-    <row r="496">
+    <row r="496" ht="28" customHeight="1">
       <c r="A496" s="2" t="n">
         <v>495</v>
       </c>
@@ -17307,7 +17357,7 @@
         </is>
       </c>
     </row>
-    <row r="497">
+    <row r="497" ht="28" customHeight="1">
       <c r="A497" s="2" t="n">
         <v>496</v>
       </c>
@@ -17341,7 +17391,7 @@
         </is>
       </c>
     </row>
-    <row r="498">
+    <row r="498" ht="28" customHeight="1">
       <c r="A498" s="2" t="n">
         <v>497</v>
       </c>
@@ -17375,7 +17425,7 @@
         </is>
       </c>
     </row>
-    <row r="499">
+    <row r="499" ht="28" customHeight="1">
       <c r="A499" s="2" t="n">
         <v>498</v>
       </c>
@@ -17409,7 +17459,7 @@
         </is>
       </c>
     </row>
-    <row r="500">
+    <row r="500" ht="28" customHeight="1">
       <c r="A500" s="2" t="n">
         <v>499</v>
       </c>
@@ -17443,7 +17493,7 @@
         </is>
       </c>
     </row>
-    <row r="501">
+    <row r="501" ht="28" customHeight="1">
       <c r="A501" s="2" t="n">
         <v>500</v>
       </c>
@@ -17477,7 +17527,7 @@
         </is>
       </c>
     </row>
-    <row r="502">
+    <row r="502" ht="28" customHeight="1">
       <c r="A502" s="2" t="n">
         <v>501</v>
       </c>
@@ -17511,7 +17561,7 @@
         </is>
       </c>
     </row>
-    <row r="503">
+    <row r="503" ht="28" customHeight="1">
       <c r="A503" s="2" t="n">
         <v>502</v>
       </c>
@@ -17545,7 +17595,7 @@
         </is>
       </c>
     </row>
-    <row r="504">
+    <row r="504" ht="28" customHeight="1">
       <c r="A504" s="2" t="n">
         <v>503</v>
       </c>
@@ -17579,7 +17629,7 @@
         </is>
       </c>
     </row>
-    <row r="505">
+    <row r="505" ht="28" customHeight="1">
       <c r="A505" s="2" t="n">
         <v>504</v>
       </c>
@@ -17613,7 +17663,7 @@
         </is>
       </c>
     </row>
-    <row r="506">
+    <row r="506" ht="28" customHeight="1">
       <c r="A506" s="2" t="n">
         <v>505</v>
       </c>
@@ -17647,7 +17697,7 @@
         </is>
       </c>
     </row>
-    <row r="507">
+    <row r="507" ht="28" customHeight="1">
       <c r="A507" s="2" t="n">
         <v>506</v>
       </c>
@@ -17681,7 +17731,7 @@
         </is>
       </c>
     </row>
-    <row r="508">
+    <row r="508" ht="28" customHeight="1">
       <c r="A508" s="2" t="n">
         <v>507</v>
       </c>
@@ -17715,7 +17765,7 @@
         </is>
       </c>
     </row>
-    <row r="509">
+    <row r="509" ht="28" customHeight="1">
       <c r="A509" s="2" t="n">
         <v>508</v>
       </c>
@@ -17749,7 +17799,7 @@
         </is>
       </c>
     </row>
-    <row r="510">
+    <row r="510" ht="28" customHeight="1">
       <c r="A510" s="2" t="n">
         <v>509</v>
       </c>
@@ -17783,7 +17833,7 @@
         </is>
       </c>
     </row>
-    <row r="511">
+    <row r="511" ht="28" customHeight="1">
       <c r="A511" s="2" t="n">
         <v>510</v>
       </c>
@@ -17817,7 +17867,7 @@
         </is>
       </c>
     </row>
-    <row r="512">
+    <row r="512" ht="28" customHeight="1">
       <c r="A512" s="2" t="n">
         <v>511</v>
       </c>
@@ -17851,7 +17901,7 @@
         </is>
       </c>
     </row>
-    <row r="513">
+    <row r="513" ht="28" customHeight="1">
       <c r="A513" s="2" t="n">
         <v>512</v>
       </c>
@@ -17885,7 +17935,7 @@
         </is>
       </c>
     </row>
-    <row r="514">
+    <row r="514" ht="28" customHeight="1">
       <c r="A514" s="2" t="n">
         <v>513</v>
       </c>
@@ -17919,7 +17969,7 @@
         </is>
       </c>
     </row>
-    <row r="515">
+    <row r="515" ht="28" customHeight="1">
       <c r="A515" s="2" t="n">
         <v>514</v>
       </c>
@@ -17953,7 +18003,7 @@
         </is>
       </c>
     </row>
-    <row r="516">
+    <row r="516" ht="28" customHeight="1">
       <c r="A516" s="2" t="n">
         <v>515</v>
       </c>
@@ -17987,7 +18037,7 @@
         </is>
       </c>
     </row>
-    <row r="517">
+    <row r="517" ht="28" customHeight="1">
       <c r="A517" s="2" t="n">
         <v>516</v>
       </c>
@@ -18021,7 +18071,7 @@
         </is>
       </c>
     </row>
-    <row r="518">
+    <row r="518" ht="28" customHeight="1">
       <c r="A518" s="2" t="n">
         <v>517</v>
       </c>
@@ -18055,7 +18105,7 @@
         </is>
       </c>
     </row>
-    <row r="519">
+    <row r="519" ht="28" customHeight="1">
       <c r="A519" s="2" t="n">
         <v>518</v>
       </c>
@@ -18089,7 +18139,7 @@
         </is>
       </c>
     </row>
-    <row r="520">
+    <row r="520" ht="28" customHeight="1">
       <c r="A520" s="2" t="n">
         <v>519</v>
       </c>
@@ -18123,7 +18173,7 @@
         </is>
       </c>
     </row>
-    <row r="521">
+    <row r="521" ht="28" customHeight="1">
       <c r="A521" s="2" t="n">
         <v>520</v>
       </c>
@@ -18157,7 +18207,7 @@
         </is>
       </c>
     </row>
-    <row r="522">
+    <row r="522" ht="28" customHeight="1">
       <c r="A522" s="2" t="n">
         <v>521</v>
       </c>
@@ -18191,7 +18241,7 @@
         </is>
       </c>
     </row>
-    <row r="523">
+    <row r="523" ht="28" customHeight="1">
       <c r="A523" s="2" t="n">
         <v>522</v>
       </c>
@@ -18225,7 +18275,7 @@
         </is>
       </c>
     </row>
-    <row r="524">
+    <row r="524" ht="28" customHeight="1">
       <c r="A524" s="2" t="n">
         <v>523</v>
       </c>
@@ -18259,7 +18309,7 @@
         </is>
       </c>
     </row>
-    <row r="525">
+    <row r="525" ht="28" customHeight="1">
       <c r="A525" s="2" t="n">
         <v>524</v>
       </c>
@@ -18293,7 +18343,7 @@
         </is>
       </c>
     </row>
-    <row r="526">
+    <row r="526" ht="28" customHeight="1">
       <c r="A526" s="2" t="n">
         <v>525</v>
       </c>
@@ -18327,7 +18377,7 @@
         </is>
       </c>
     </row>
-    <row r="527">
+    <row r="527" ht="28" customHeight="1">
       <c r="A527" s="2" t="n">
         <v>526</v>
       </c>
@@ -18361,7 +18411,7 @@
         </is>
       </c>
     </row>
-    <row r="528">
+    <row r="528" ht="28" customHeight="1">
       <c r="A528" s="2" t="n">
         <v>527</v>
       </c>
@@ -18395,7 +18445,7 @@
         </is>
       </c>
     </row>
-    <row r="529">
+    <row r="529" ht="28" customHeight="1">
       <c r="A529" s="2" t="n">
         <v>528</v>
       </c>
@@ -18429,7 +18479,7 @@
         </is>
       </c>
     </row>
-    <row r="530">
+    <row r="530" ht="28" customHeight="1">
       <c r="A530" s="2" t="n">
         <v>529</v>
       </c>
@@ -18440,12 +18490,12 @@
       </c>
       <c r="C530" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /index:\u65b0\u5efa CAN \u8fde\u63a5</t>
+          <t>关键元素 /index:新建 CAN 连接</t>
         </is>
       </c>
       <c r="D530" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/index:\u65b0\u5efa CAN \u8fde\u63a5</t>
+          <t>关键元素可见：/index:新建 CAN 连接</t>
         </is>
       </c>
       <c r="E530" s="2" t="n"/>
@@ -18463,7 +18513,7 @@
         </is>
       </c>
     </row>
-    <row r="531">
+    <row r="531" ht="28" customHeight="1">
       <c r="A531" s="2" t="n">
         <v>530</v>
       </c>
@@ -18474,12 +18524,12 @@
       </c>
       <c r="C531" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /index:\u65b0\u5efa UDP \u8fde\u63a5</t>
+          <t>关键元素 /index:新建 UDP 连接</t>
         </is>
       </c>
       <c r="D531" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/index:\u65b0\u5efa UDP \u8fde\u63a5</t>
+          <t>关键元素可见：/index:新建 UDP 连接</t>
         </is>
       </c>
       <c r="E531" s="2" t="n"/>
@@ -18497,7 +18547,7 @@
         </is>
       </c>
     </row>
-    <row r="532">
+    <row r="532" ht="28" customHeight="1">
       <c r="A532" s="2" t="n">
         <v>531</v>
       </c>
@@ -18508,12 +18558,12 @@
       </c>
       <c r="C532" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /index:\u65b0\u5efa\u4e32\u53e3\u8fde\u63a5</t>
+          <t>关键元素 /index:新建串口连接</t>
         </is>
       </c>
       <c r="D532" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/index:\u65b0\u5efa\u4e32\u53e3\u8fde\u63a5</t>
+          <t>关键元素可见：/index:新建串口连接</t>
         </is>
       </c>
       <c r="E532" s="2" t="n"/>
@@ -18531,7 +18581,7 @@
         </is>
       </c>
     </row>
-    <row r="533">
+    <row r="533" ht="28" customHeight="1">
       <c r="A533" s="2" t="n">
         <v>532</v>
       </c>
@@ -18542,12 +18592,12 @@
       </c>
       <c r="C533" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /index:\u91c7\u96c6\u8bbe\u5907</t>
+          <t>关键元素 /index:采集设备</t>
         </is>
       </c>
       <c r="D533" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/index:\u91c7\u96c6\u8bbe\u5907</t>
+          <t>关键元素可见：/index:采集设备</t>
         </is>
       </c>
       <c r="E533" s="2" t="n"/>
@@ -18565,7 +18615,7 @@
         </is>
       </c>
     </row>
-    <row r="534">
+    <row r="534" ht="28" customHeight="1">
       <c r="A534" s="2" t="n">
         <v>533</v>
       </c>
@@ -18576,12 +18626,12 @@
       </c>
       <c r="C534" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /index:\u8bbe\u5907\u670d\u52a1</t>
+          <t>关键元素 /index:设备服务</t>
         </is>
       </c>
       <c r="D534" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/index:\u8bbe\u5907\u670d\u52a1</t>
+          <t>关键元素可见：/index:设备服务</t>
         </is>
       </c>
       <c r="E534" s="2" t="n"/>
@@ -18599,7 +18649,7 @@
         </is>
       </c>
     </row>
-    <row r="535">
+    <row r="535" ht="28" customHeight="1">
       <c r="A535" s="2" t="n">
         <v>534</v>
       </c>
@@ -18610,12 +18660,12 @@
       </c>
       <c r="C535" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /index:\u5173\u95ed\u6240\u6709\u8fde\u63a5</t>
+          <t>关键元素 /index:关闭所有连接</t>
         </is>
       </c>
       <c r="D535" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/index:\u5173\u95ed\u6240\u6709\u8fde\u63a5</t>
+          <t>关键元素可见：/index:关闭所有连接</t>
         </is>
       </c>
       <c r="E535" s="2" t="n"/>
@@ -18633,7 +18683,7 @@
         </is>
       </c>
     </row>
-    <row r="536">
+    <row r="536" ht="42" customHeight="1">
       <c r="A536" s="2" t="n">
         <v>535</v>
       </c>
@@ -18644,12 +18694,12 @@
       </c>
       <c r="C536" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /biu/telecontrol/control:\u65b0\u5efaCAN\u8fde\u63a5-A</t>
+          <t>关键元素 /biu/telecontrol/control:新建CAN连接-A</t>
         </is>
       </c>
       <c r="D536" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/biu/telecontrol/control:\u65b0\u5efaCAN\u8fde\u63a5-A</t>
+          <t>关键元素可见：/biu/telecontrol/control:新建CAN连接-A</t>
         </is>
       </c>
       <c r="E536" s="2" t="n"/>
@@ -18667,7 +18717,7 @@
         </is>
       </c>
     </row>
-    <row r="537">
+    <row r="537" ht="42" customHeight="1">
       <c r="A537" s="2" t="n">
         <v>536</v>
       </c>
@@ -18678,12 +18728,12 @@
       </c>
       <c r="C537" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /biu/telecontrol/control:\u65b0\u5efaCAN\u8fde\u63a5-B</t>
+          <t>关键元素 /biu/telecontrol/control:新建CAN连接-B</t>
         </is>
       </c>
       <c r="D537" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/biu/telecontrol/control:\u65b0\u5efaCAN\u8fde\u63a5-B</t>
+          <t>关键元素可见：/biu/telecontrol/control:新建CAN连接-B</t>
         </is>
       </c>
       <c r="E537" s="2" t="n"/>
@@ -18701,7 +18751,7 @@
         </is>
       </c>
     </row>
-    <row r="538">
+    <row r="538" ht="42" customHeight="1">
       <c r="A538" s="2" t="n">
         <v>537</v>
       </c>
@@ -18712,12 +18762,12 @@
       </c>
       <c r="C538" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /biu/telecontrol/control:\u53d1\u9001\u9065\u6d4b\u8bf7\u6c42</t>
+          <t>关键元素 /biu/telecontrol/control:发送遥测请求</t>
         </is>
       </c>
       <c r="D538" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/biu/telecontrol/control:\u53d1\u9001\u9065\u6d4b\u8bf7\u6c42</t>
+          <t>关键元素可见：/biu/telecontrol/control:发送遥测请求</t>
         </is>
       </c>
       <c r="E538" s="2" t="n"/>
@@ -18735,7 +18785,7 @@
         </is>
       </c>
     </row>
-    <row r="539">
+    <row r="539" ht="28" customHeight="1">
       <c r="A539" s="2" t="n">
         <v>538</v>
       </c>
@@ -18746,12 +18796,12 @@
       </c>
       <c r="C539" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /biu/telecontrol/control:\u76ee\u6807\u5730\u5740</t>
+          <t>关键元素 /biu/telecontrol/control:目标地址</t>
         </is>
       </c>
       <c r="D539" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/biu/telecontrol/control:\u76ee\u6807\u5730\u5740</t>
+          <t>关键元素可见：/biu/telecontrol/control:目标地址</t>
         </is>
       </c>
       <c r="E539" s="2" t="n"/>
@@ -18769,7 +18819,7 @@
         </is>
       </c>
     </row>
-    <row r="540">
+    <row r="540" ht="28" customHeight="1">
       <c r="A540" s="2" t="n">
         <v>539</v>
       </c>
@@ -18780,12 +18830,12 @@
       </c>
       <c r="C540" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /biu/telecontrol/control:\u5b9a\u65f6\u9065\u6d4b</t>
+          <t>关键元素 /biu/telecontrol/control:定时遥测</t>
         </is>
       </c>
       <c r="D540" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/biu/telecontrol/control:\u5b9a\u65f6\u9065\u6d4b</t>
+          <t>关键元素可见：/biu/telecontrol/control:定时遥测</t>
         </is>
       </c>
       <c r="E540" s="2" t="n"/>
@@ -18803,7 +18853,7 @@
         </is>
       </c>
     </row>
-    <row r="541">
+    <row r="541" ht="42" customHeight="1">
       <c r="A541" s="2" t="n">
         <v>540</v>
       </c>
@@ -18814,12 +18864,12 @@
       </c>
       <c r="C541" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /xl/telecontrol/control:\u65b0\u5efaCAN\u8fde\u63a5-A</t>
+          <t>关键元素 /xl/telecontrol/control:新建CAN连接-A</t>
         </is>
       </c>
       <c r="D541" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/xl/telecontrol/control:\u65b0\u5efaCAN\u8fde\u63a5-A</t>
+          <t>关键元素可见：/xl/telecontrol/control:新建CAN连接-A</t>
         </is>
       </c>
       <c r="E541" s="2" t="n"/>
@@ -18837,7 +18887,7 @@
         </is>
       </c>
     </row>
-    <row r="542">
+    <row r="542" ht="42" customHeight="1">
       <c r="A542" s="2" t="n">
         <v>541</v>
       </c>
@@ -18848,12 +18898,12 @@
       </c>
       <c r="C542" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /xl/telecontrol/control:\u65b0\u5efaCAN\u8fde\u63a5-B</t>
+          <t>关键元素 /xl/telecontrol/control:新建CAN连接-B</t>
         </is>
       </c>
       <c r="D542" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/xl/telecontrol/control:\u65b0\u5efaCAN\u8fde\u63a5-B</t>
+          <t>关键元素可见：/xl/telecontrol/control:新建CAN连接-B</t>
         </is>
       </c>
       <c r="E542" s="2" t="n"/>
@@ -18871,7 +18921,7 @@
         </is>
       </c>
     </row>
-    <row r="543">
+    <row r="543" ht="42" customHeight="1">
       <c r="A543" s="2" t="n">
         <v>542</v>
       </c>
@@ -18882,12 +18932,12 @@
       </c>
       <c r="C543" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /xl/telecontrol/control:\u53d1\u9001\u9065\u6d4b\u8bf7\u6c42</t>
+          <t>关键元素 /xl/telecontrol/control:发送遥测请求</t>
         </is>
       </c>
       <c r="D543" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/xl/telecontrol/control:\u53d1\u9001\u9065\u6d4b\u8bf7\u6c42</t>
+          <t>关键元素可见：/xl/telecontrol/control:发送遥测请求</t>
         </is>
       </c>
       <c r="E543" s="2" t="n"/>
@@ -18905,7 +18955,7 @@
         </is>
       </c>
     </row>
-    <row r="544">
+    <row r="544" ht="42" customHeight="1">
       <c r="A544" s="2" t="n">
         <v>543</v>
       </c>
@@ -18916,12 +18966,12 @@
       </c>
       <c r="C544" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /xl/telecontrol/control:\u65f6\u95f4\u540c\u6b65 GNSS \u6709\u6548</t>
+          <t>关键元素 /xl/telecontrol/control:时间同步 GNSS 有效</t>
         </is>
       </c>
       <c r="D544" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/xl/telecontrol/control:\u65f6\u95f4\u540c\u6b65 GNSS \u6709\u6548</t>
+          <t>关键元素可见：/xl/telecontrol/control:时间同步 GNSS 有效</t>
         </is>
       </c>
       <c r="E544" s="2" t="n"/>
@@ -18939,7 +18989,7 @@
         </is>
       </c>
     </row>
-    <row r="545">
+    <row r="545" ht="28" customHeight="1">
       <c r="A545" s="2" t="n">
         <v>544</v>
       </c>
@@ -18950,12 +19000,12 @@
       </c>
       <c r="C545" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /xl/telecontrol/control:\u5b9a\u65f6\u9065\u6d4b</t>
+          <t>关键元素 /xl/telecontrol/control:定时遥测</t>
         </is>
       </c>
       <c r="D545" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/xl/telecontrol/control:\u5b9a\u65f6\u9065\u6d4b</t>
+          <t>关键元素可见：/xl/telecontrol/control:定时遥测</t>
         </is>
       </c>
       <c r="E545" s="2" t="n"/>
@@ -18973,7 +19023,7 @@
         </is>
       </c>
     </row>
-    <row r="546">
+    <row r="546" ht="42" customHeight="1">
       <c r="A546" s="2" t="n">
         <v>545</v>
       </c>
@@ -18984,12 +19034,12 @@
       </c>
       <c r="C546" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /yj216/telecontrol/control:\u65b0\u5efaCAN\u8fde\u63a5-A</t>
+          <t>关键元素 /yj216/telecontrol/control:新建CAN连接-A</t>
         </is>
       </c>
       <c r="D546" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/yj216/telecontrol/control:\u65b0\u5efaCAN\u8fde\u63a5-A</t>
+          <t>关键元素可见：/yj216/telecontrol/control:新建CAN连接-A</t>
         </is>
       </c>
       <c r="E546" s="2" t="n"/>
@@ -19007,7 +19057,7 @@
         </is>
       </c>
     </row>
-    <row r="547">
+    <row r="547" ht="42" customHeight="1">
       <c r="A547" s="2" t="n">
         <v>546</v>
       </c>
@@ -19018,12 +19068,12 @@
       </c>
       <c r="C547" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /yj216/telecontrol/control:\u65b0\u5efaCAN\u8fde\u63a5-B</t>
+          <t>关键元素 /yj216/telecontrol/control:新建CAN连接-B</t>
         </is>
       </c>
       <c r="D547" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/yj216/telecontrol/control:\u65b0\u5efaCAN\u8fde\u63a5-B</t>
+          <t>关键元素可见：/yj216/telecontrol/control:新建CAN连接-B</t>
         </is>
       </c>
       <c r="E547" s="2" t="n"/>
@@ -19041,7 +19091,7 @@
         </is>
       </c>
     </row>
-    <row r="548">
+    <row r="548" ht="42" customHeight="1">
       <c r="A548" s="2" t="n">
         <v>547</v>
       </c>
@@ -19052,12 +19102,12 @@
       </c>
       <c r="C548" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /yj216/telecontrol/control:\u53d1\u9001\u9065\u6d4b\u8bf7\u6c42</t>
+          <t>关键元素 /yj216/telecontrol/control:发送遥测请求</t>
         </is>
       </c>
       <c r="D548" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/yj216/telecontrol/control:\u53d1\u9001\u9065\u6d4b\u8bf7\u6c42</t>
+          <t>关键元素可见：/yj216/telecontrol/control:发送遥测请求</t>
         </is>
       </c>
       <c r="E548" s="2" t="n"/>
@@ -19075,7 +19125,7 @@
         </is>
       </c>
     </row>
-    <row r="549">
+    <row r="549" ht="28" customHeight="1">
       <c r="A549" s="2" t="n">
         <v>548</v>
       </c>
@@ -19086,12 +19136,12 @@
       </c>
       <c r="C549" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /biu/telecontrol/command:\u53d1\u9001\u6307\u4ee4</t>
+          <t>关键元素 /biu/telecontrol/command:发送指令</t>
         </is>
       </c>
       <c r="D549" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/biu/telecontrol/command:\u53d1\u9001\u6307\u4ee4</t>
+          <t>关键元素可见：/biu/telecontrol/command:发送指令</t>
         </is>
       </c>
       <c r="E549" s="2" t="n"/>
@@ -19109,7 +19159,7 @@
         </is>
       </c>
     </row>
-    <row r="550">
+    <row r="550" ht="28" customHeight="1">
       <c r="A550" s="2" t="n">
         <v>549</v>
       </c>
@@ -19120,12 +19170,12 @@
       </c>
       <c r="C550" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /biu/telecontrol/command:\u9884\u89c8\u7ec4\u5e27</t>
+          <t>关键元素 /biu/telecontrol/command:预览组帧</t>
         </is>
       </c>
       <c r="D550" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/biu/telecontrol/command:\u9884\u89c8\u7ec4\u5e27</t>
+          <t>关键元素可见：/biu/telecontrol/command:预览组帧</t>
         </is>
       </c>
       <c r="E550" s="2" t="n"/>
@@ -19143,7 +19193,7 @@
         </is>
       </c>
     </row>
-    <row r="551">
+    <row r="551" ht="28" customHeight="1">
       <c r="A551" s="2" t="n">
         <v>550</v>
       </c>
@@ -19154,12 +19204,12 @@
       </c>
       <c r="C551" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /xl/telecontrol/command:\u53d1\u9001\u6307\u4ee4</t>
+          <t>关键元素 /xl/telecontrol/command:发送指令</t>
         </is>
       </c>
       <c r="D551" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/xl/telecontrol/command:\u53d1\u9001\u6307\u4ee4</t>
+          <t>关键元素可见：/xl/telecontrol/command:发送指令</t>
         </is>
       </c>
       <c r="E551" s="2" t="n"/>
@@ -19177,7 +19227,7 @@
         </is>
       </c>
     </row>
-    <row r="552">
+    <row r="552" ht="28" customHeight="1">
       <c r="A552" s="2" t="n">
         <v>551</v>
       </c>
@@ -19188,12 +19238,12 @@
       </c>
       <c r="C552" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /xl/telecontrol/command:\u9884\u89c8\u7ec4\u5e27</t>
+          <t>关键元素 /xl/telecontrol/command:预览组帧</t>
         </is>
       </c>
       <c r="D552" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/xl/telecontrol/command:\u9884\u89c8\u7ec4\u5e27</t>
+          <t>关键元素可见：/xl/telecontrol/command:预览组帧</t>
         </is>
       </c>
       <c r="E552" s="2" t="n"/>
@@ -19211,7 +19261,7 @@
         </is>
       </c>
     </row>
-    <row r="553">
+    <row r="553" ht="42" customHeight="1">
       <c r="A553" s="2" t="n">
         <v>552</v>
       </c>
@@ -19222,12 +19272,12 @@
       </c>
       <c r="C553" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /yj216/telecontrol/command:\u53d1\u9001\u6307\u4ee4</t>
+          <t>关键元素 /yj216/telecontrol/command:发送指令</t>
         </is>
       </c>
       <c r="D553" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/yj216/telecontrol/command:\u53d1\u9001\u6307\u4ee4</t>
+          <t>关键元素可见：/yj216/telecontrol/command:发送指令</t>
         </is>
       </c>
       <c r="E553" s="2" t="n"/>
@@ -19245,7 +19295,7 @@
         </is>
       </c>
     </row>
-    <row r="554">
+    <row r="554" ht="42" customHeight="1">
       <c r="A554" s="2" t="n">
         <v>553</v>
       </c>
@@ -19256,12 +19306,12 @@
       </c>
       <c r="C554" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /yj216/telecontrol/command:\u9884\u89c8\u7ec4\u5e27</t>
+          <t>关键元素 /yj216/telecontrol/command:预览组帧</t>
         </is>
       </c>
       <c r="D554" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/yj216/telecontrol/command:\u9884\u89c8\u7ec4\u5e27</t>
+          <t>关键元素可见：/yj216/telecontrol/command:预览组帧</t>
         </is>
       </c>
       <c r="E554" s="2" t="n"/>
@@ -19279,7 +19329,7 @@
         </is>
       </c>
     </row>
-    <row r="555">
+    <row r="555" ht="28" customHeight="1">
       <c r="A555" s="2" t="n">
         <v>554</v>
       </c>
@@ -19290,12 +19340,12 @@
       </c>
       <c r="C555" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /biu/telecontrol/sequence:\u65b0\u589e</t>
+          <t>关键元素 /biu/telecontrol/sequence:新增</t>
         </is>
       </c>
       <c r="D555" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/biu/telecontrol/sequence:\u65b0\u589e</t>
+          <t>关键元素可见：/biu/telecontrol/sequence:新增</t>
         </is>
       </c>
       <c r="E555" s="2" t="n"/>
@@ -19313,7 +19363,7 @@
         </is>
       </c>
     </row>
-    <row r="556">
+    <row r="556" ht="28" customHeight="1">
       <c r="A556" s="2" t="n">
         <v>555</v>
       </c>
@@ -19324,12 +19374,12 @@
       </c>
       <c r="C556" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /xl/telecontrol/sequence:\u65b0\u589e</t>
+          <t>关键元素 /xl/telecontrol/sequence:新增</t>
         </is>
       </c>
       <c r="D556" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/xl/telecontrol/sequence:\u65b0\u589e</t>
+          <t>关键元素可见：/xl/telecontrol/sequence:新增</t>
         </is>
       </c>
       <c r="E556" s="2" t="n"/>
@@ -19347,7 +19397,7 @@
         </is>
       </c>
     </row>
-    <row r="557">
+    <row r="557" ht="28" customHeight="1">
       <c r="A557" s="2" t="n">
         <v>556</v>
       </c>
@@ -19358,12 +19408,12 @@
       </c>
       <c r="C557" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /yj216/telecontrol/sequence:\u65b0\u589e</t>
+          <t>关键元素 /yj216/telecontrol/sequence:新增</t>
         </is>
       </c>
       <c r="D557" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/yj216/telecontrol/sequence:\u65b0\u589e</t>
+          <t>关键元素可见：/yj216/telecontrol/sequence:新增</t>
         </is>
       </c>
       <c r="E557" s="2" t="n"/>
@@ -19381,7 +19431,7 @@
         </is>
       </c>
     </row>
-    <row r="558">
+    <row r="558" ht="42" customHeight="1">
       <c r="A558" s="2" t="n">
         <v>557</v>
       </c>
@@ -19392,12 +19442,12 @@
       </c>
       <c r="C558" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /xl/board/camera:\u65b0\u5efa\u63a7\u5236\u4e32\u53e3\u8fde\u63a5</t>
+          <t>关键元素 /xl/board/camera:新建控制串口连接</t>
         </is>
       </c>
       <c r="D558" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/xl/board/camera:\u65b0\u5efa\u63a7\u5236\u4e32\u53e3\u8fde\u63a5</t>
+          <t>关键元素可见：/xl/board/camera:新建控制串口连接</t>
         </is>
       </c>
       <c r="E558" s="2" t="n"/>
@@ -19415,7 +19465,7 @@
         </is>
       </c>
     </row>
-    <row r="559">
+    <row r="559" ht="42" customHeight="1">
       <c r="A559" s="2" t="n">
         <v>558</v>
       </c>
@@ -19426,12 +19476,12 @@
       </c>
       <c r="C559" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /xl/board/camera:\u65b0\u5efa\u56fe\u50cf\u4e32\u53e3\u8fde\u63a5</t>
+          <t>关键元素 /xl/board/camera:新建图像串口连接</t>
         </is>
       </c>
       <c r="D559" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/xl/board/camera:\u65b0\u5efa\u56fe\u50cf\u4e32\u53e3\u8fde\u63a5</t>
+          <t>关键元素可见：/xl/board/camera:新建图像串口连接</t>
         </is>
       </c>
       <c r="E559" s="2" t="n"/>
@@ -19449,7 +19499,7 @@
         </is>
       </c>
     </row>
-    <row r="560">
+    <row r="560" ht="42" customHeight="1">
       <c r="A560" s="2" t="n">
         <v>559</v>
       </c>
@@ -19460,12 +19510,12 @@
       </c>
       <c r="C560" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /xl/board/camera_v17:\u65b0\u5efa\u63a7\u5236\u4e32\u53e3\u8fde\u63a5</t>
+          <t>关键元素 /xl/board/camera_v17:新建控制串口连接</t>
         </is>
       </c>
       <c r="D560" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/xl/board/camera_v17:\u65b0\u5efa\u63a7\u5236\u4e32\u53e3\u8fde\u63a5</t>
+          <t>关键元素可见：/xl/board/camera_v17:新建控制串口连接</t>
         </is>
       </c>
       <c r="E560" s="2" t="n"/>
@@ -19483,7 +19533,7 @@
         </is>
       </c>
     </row>
-    <row r="561">
+    <row r="561" ht="42" customHeight="1">
       <c r="A561" s="2" t="n">
         <v>560</v>
       </c>
@@ -19494,12 +19544,12 @@
       </c>
       <c r="C561" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /xl/board/camera_v17:\u65b0\u5efa\u56fe\u50cf\u4e32\u53e3\u8fde\u63a5</t>
+          <t>关键元素 /xl/board/camera_v17:新建图像串口连接</t>
         </is>
       </c>
       <c r="D561" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/xl/board/camera_v17:\u65b0\u5efa\u56fe\u50cf\u4e32\u53e3\u8fde\u63a5</t>
+          <t>关键元素可见：/xl/board/camera_v17:新建图像串口连接</t>
         </is>
       </c>
       <c r="E561" s="2" t="n"/>
@@ -19517,7 +19567,7 @@
         </is>
       </c>
     </row>
-    <row r="562">
+    <row r="562" ht="42" customHeight="1">
       <c r="A562" s="2" t="n">
         <v>561</v>
       </c>
@@ -19528,12 +19578,12 @@
       </c>
       <c r="C562" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /xl/board/rkdj:\u65b0\u5efa\u4e32\u53e3\u8fde\u63a5</t>
+          <t>关键元素 /xl/board/rkdj:新建串口连接</t>
         </is>
       </c>
       <c r="D562" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/xl/board/rkdj:\u65b0\u5efa\u4e32\u53e3\u8fde\u63a5</t>
+          <t>关键元素可见：/xl/board/rkdj:新建串口连接</t>
         </is>
       </c>
       <c r="E562" s="2" t="n"/>
@@ -19551,7 +19601,7 @@
         </is>
       </c>
     </row>
-    <row r="563">
+    <row r="563" ht="28" customHeight="1">
       <c r="A563" s="2" t="n">
         <v>562</v>
       </c>
@@ -19562,12 +19612,12 @@
       </c>
       <c r="C563" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /xl/board/zk:\u65b0\u5efa\u4e32\u53e3\u8fde\u63a5</t>
+          <t>关键元素 /xl/board/zk:新建串口连接</t>
         </is>
       </c>
       <c r="D563" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/xl/board/zk:\u65b0\u5efa\u4e32\u53e3\u8fde\u63a5</t>
+          <t>关键元素可见：/xl/board/zk:新建串口连接</t>
         </is>
       </c>
       <c r="E563" s="2" t="n"/>
@@ -19585,7 +19635,7 @@
         </is>
       </c>
     </row>
-    <row r="564">
+    <row r="564" ht="42" customHeight="1">
       <c r="A564" s="2" t="n">
         <v>563</v>
       </c>
@@ -19596,12 +19646,12 @@
       </c>
       <c r="C564" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /xl/board/cpazx:\u65b0\u5efa\u4e32\u53e3\u8fde\u63a5</t>
+          <t>关键元素 /xl/board/cpazx:新建串口连接</t>
         </is>
       </c>
       <c r="D564" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/xl/board/cpazx:\u65b0\u5efa\u4e32\u53e3\u8fde\u63a5</t>
+          <t>关键元素可见：/xl/board/cpazx:新建串口连接</t>
         </is>
       </c>
       <c r="E564" s="2" t="n"/>
@@ -19619,7 +19669,7 @@
         </is>
       </c>
     </row>
-    <row r="565">
+    <row r="565" ht="28" customHeight="1">
       <c r="A565" s="2" t="n">
         <v>564</v>
       </c>
@@ -19630,12 +19680,12 @@
       </c>
       <c r="C565" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /xl/board/dj:\u65b0\u5efa UDP \u8fde\u63a5</t>
+          <t>关键元素 /xl/board/dj:新建 UDP 连接</t>
         </is>
       </c>
       <c r="D565" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/xl/board/dj:\u65b0\u5efa UDP \u8fde\u63a5</t>
+          <t>关键元素可见：/xl/board/dj:新建 UDP 连接</t>
         </is>
       </c>
       <c r="E565" s="2" t="n"/>
@@ -19653,7 +19703,7 @@
         </is>
       </c>
     </row>
-    <row r="566">
+    <row r="566" ht="28" customHeight="1">
       <c r="A566" s="2" t="n">
         <v>565</v>
       </c>
@@ -19664,12 +19714,12 @@
       </c>
       <c r="C566" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /yj216/rs422:\u65b0\u5efa\u4e32\u53e3\u8fde\u63a5</t>
+          <t>关键元素 /yj216/rs422:新建串口连接</t>
         </is>
       </c>
       <c r="D566" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/yj216/rs422:\u65b0\u5efa\u4e32\u53e3\u8fde\u63a5</t>
+          <t>关键元素可见：/yj216/rs422:新建串口连接</t>
         </is>
       </c>
       <c r="E566" s="2" t="n"/>
@@ -19687,7 +19737,7 @@
         </is>
       </c>
     </row>
-    <row r="567">
+    <row r="567" ht="28" customHeight="1">
       <c r="A567" s="2" t="n">
         <v>566</v>
       </c>
@@ -19698,12 +19748,12 @@
       </c>
       <c r="C567" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /telemetry/live:\u8868\u7c7b\u578b</t>
+          <t>关键元素 /telemetry/live:表类型</t>
         </is>
       </c>
       <c r="D567" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/telemetry/live:\u8868\u7c7b\u578b</t>
+          <t>关键元素可见：/telemetry/live:表类型</t>
         </is>
       </c>
       <c r="E567" s="2" t="n"/>
@@ -19721,7 +19771,7 @@
         </is>
       </c>
     </row>
-    <row r="568">
+    <row r="568" ht="28" customHeight="1">
       <c r="A568" s="2" t="n">
         <v>567</v>
       </c>
@@ -19732,12 +19782,12 @@
       </c>
       <c r="C568" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /telemetry/curve:\u6dfb\u52a0</t>
+          <t>关键元素 /telemetry/curve:添加</t>
         </is>
       </c>
       <c r="D568" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/telemetry/curve:\u6dfb\u52a0</t>
+          <t>关键元素可见：/telemetry/curve:添加</t>
         </is>
       </c>
       <c r="E568" s="2" t="n"/>
@@ -19755,7 +19805,7 @@
         </is>
       </c>
     </row>
-    <row r="569">
+    <row r="569" ht="42" customHeight="1">
       <c r="A569" s="2" t="n">
         <v>568</v>
       </c>
@@ -19766,12 +19816,12 @@
       </c>
       <c r="C569" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /telemetry/archive:\u518d\u9009\u62e9\u65f6\u95f4\u533a\u95f4\u67e5\u8be2</t>
+          <t>关键元素 /telemetry/archive:再选择时间区间查询</t>
         </is>
       </c>
       <c r="D569" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/telemetry/archive:\u518d\u9009\u62e9\u65f6\u95f4\u533a\u95f4\u67e5\u8be2</t>
+          <t>关键元素可见：/telemetry/archive:再选择时间区间查询</t>
         </is>
       </c>
       <c r="E569" s="2" t="n"/>
@@ -19789,7 +19839,7 @@
         </is>
       </c>
     </row>
-    <row r="570">
+    <row r="570" ht="28" customHeight="1">
       <c r="A570" s="2" t="n">
         <v>569</v>
       </c>
@@ -19800,12 +19850,12 @@
       </c>
       <c r="C570" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /telemetry/canHistory:\u89e3\u6790</t>
+          <t>关键元素 /telemetry/canHistory:解析</t>
         </is>
       </c>
       <c r="D570" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/telemetry/canHistory:\u89e3\u6790</t>
+          <t>关键元素可见：/telemetry/canHistory:解析</t>
         </is>
       </c>
       <c r="E570" s="2" t="n"/>
@@ -19823,7 +19873,7 @@
         </is>
       </c>
     </row>
-    <row r="571">
+    <row r="571" ht="28" customHeight="1">
       <c r="A571" s="2" t="n">
         <v>570</v>
       </c>
@@ -19834,12 +19884,12 @@
       </c>
       <c r="C571" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /telemetry/fileHistory:\u89e3\u6790</t>
+          <t>关键元素 /telemetry/fileHistory:解析</t>
         </is>
       </c>
       <c r="D571" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/telemetry/fileHistory:\u89e3\u6790</t>
+          <t>关键元素可见：/telemetry/fileHistory:解析</t>
         </is>
       </c>
       <c r="E571" s="2" t="n"/>
@@ -19857,7 +19907,7 @@
         </is>
       </c>
     </row>
-    <row r="572">
+    <row r="572" ht="28" customHeight="1">
       <c r="A572" s="2" t="n">
         <v>571</v>
       </c>
@@ -19868,12 +19918,12 @@
       </c>
       <c r="C572" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /telemetry/fileCurve:\u67e5\u8be2</t>
+          <t>关键元素 /telemetry/fileCurve:查询</t>
         </is>
       </c>
       <c r="D572" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/telemetry/fileCurve:\u67e5\u8be2</t>
+          <t>关键元素可见：/telemetry/fileCurve:查询</t>
         </is>
       </c>
       <c r="E572" s="2" t="n"/>
@@ -19891,7 +19941,7 @@
         </is>
       </c>
     </row>
-    <row r="573">
+    <row r="573" ht="42" customHeight="1">
       <c r="A573" s="2" t="n">
         <v>572</v>
       </c>
@@ -19902,12 +19952,12 @@
       </c>
       <c r="C573" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /debug/simulate:\u901a\u7528\u6570\u636e\u53d1\u9001\u6a21\u62df</t>
+          <t>关键元素 /debug/simulate:通用数据发送模拟</t>
         </is>
       </c>
       <c r="D573" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/debug/simulate:\u901a\u7528\u6570\u636e\u53d1\u9001\u6a21\u62df</t>
+          <t>关键元素可见：/debug/simulate:通用数据发送模拟</t>
         </is>
       </c>
       <c r="E573" s="2" t="n"/>
@@ -19925,7 +19975,7 @@
         </is>
       </c>
     </row>
-    <row r="574">
+    <row r="574" ht="42" customHeight="1">
       <c r="A574" s="2" t="n">
         <v>573</v>
       </c>
@@ -19936,12 +19986,12 @@
       </c>
       <c r="C574" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /debug/simulate:BIU-CAN\u9065\u6d4b\u590d\u5408\u5e27\u6570\u636e\u6a21\u62df</t>
+          <t>关键元素 /debug/simulate:BIU-CAN遥测复合帧数据模拟</t>
         </is>
       </c>
       <c r="D574" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/debug/simulate:BIU-CAN\u9065\u6d4b\u590d\u5408\u5e27\u6570\u636e\u6a21\u62df</t>
+          <t>关键元素可见：/debug/simulate:BIU-CAN遥测复合帧数据模拟</t>
         </is>
       </c>
       <c r="E574" s="2" t="n"/>
@@ -19959,7 +20009,7 @@
         </is>
       </c>
     </row>
-    <row r="575">
+    <row r="575" ht="28" customHeight="1">
       <c r="A575" s="2" t="n">
         <v>574</v>
       </c>
@@ -19970,12 +20020,12 @@
       </c>
       <c r="C575" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /debug/simulate:\u5e27\u7ec4\u88c5\u7c7b\u578b</t>
+          <t>关键元素 /debug/simulate:帧组装类型</t>
         </is>
       </c>
       <c r="D575" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/debug/simulate:\u5e27\u7ec4\u88c5\u7c7b\u578b</t>
+          <t>关键元素可见：/debug/simulate:帧组装类型</t>
         </is>
       </c>
       <c r="E575" s="2" t="n"/>
@@ -19993,7 +20043,7 @@
         </is>
       </c>
     </row>
-    <row r="576">
+    <row r="576" ht="28" customHeight="1">
       <c r="A576" s="2" t="n">
         <v>575</v>
       </c>
@@ -20004,12 +20054,12 @@
       </c>
       <c r="C576" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /debug/simulate:\u5e27\u89e3\u6790\u7c7b\u578b</t>
+          <t>关键元素 /debug/simulate:帧解析类型</t>
         </is>
       </c>
       <c r="D576" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/debug/simulate:\u5e27\u89e3\u6790\u7c7b\u578b</t>
+          <t>关键元素可见：/debug/simulate:帧解析类型</t>
         </is>
       </c>
       <c r="E576" s="2" t="n"/>
@@ -20027,7 +20077,7 @@
         </is>
       </c>
     </row>
-    <row r="577">
+    <row r="577" ht="28" customHeight="1">
       <c r="A577" s="2" t="n">
         <v>576</v>
       </c>
@@ -20038,12 +20088,12 @@
       </c>
       <c r="C577" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /debug/simulate:\u5f00\u59cb\u6a21\u62df</t>
+          <t>关键元素 /debug/simulate:开始模拟</t>
         </is>
       </c>
       <c r="D577" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/debug/simulate:\u5f00\u59cb\u6a21\u62df</t>
+          <t>关键元素可见：/debug/simulate:开始模拟</t>
         </is>
       </c>
       <c r="E577" s="2" t="n"/>
@@ -20061,7 +20111,7 @@
         </is>
       </c>
     </row>
-    <row r="578">
+    <row r="578" ht="28" customHeight="1">
       <c r="A578" s="2" t="n">
         <v>577</v>
       </c>
@@ -20072,12 +20122,12 @@
       </c>
       <c r="C578" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /debug/simulate:\u586b\u5165\u6837\u4f8b</t>
+          <t>关键元素 /debug/simulate:填入样例</t>
         </is>
       </c>
       <c r="D578" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/debug/simulate:\u586b\u5165\u6837\u4f8b</t>
+          <t>关键元素可见：/debug/simulate:填入样例</t>
         </is>
       </c>
       <c r="E578" s="2" t="n"/>
@@ -20095,7 +20145,7 @@
         </is>
       </c>
     </row>
-    <row r="579">
+    <row r="579" ht="28" customHeight="1">
       <c r="A579" s="2" t="n">
         <v>578</v>
       </c>
@@ -20106,12 +20156,12 @@
       </c>
       <c r="C579" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /debug/simulate:\u6e05\u7a7a</t>
+          <t>关键元素 /debug/simulate:清空</t>
         </is>
       </c>
       <c r="D579" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/debug/simulate:\u6e05\u7a7a</t>
+          <t>关键元素可见：/debug/simulate:清空</t>
         </is>
       </c>
       <c r="E579" s="2" t="n"/>
@@ -20129,7 +20179,7 @@
         </is>
       </c>
     </row>
-    <row r="580">
+    <row r="580" ht="28" customHeight="1">
       <c r="A580" s="2" t="n">
         <v>579</v>
       </c>
@@ -20140,12 +20190,12 @@
       </c>
       <c r="C580" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /debug/xfer:\u5237\u65b0\u8bbe\u5907</t>
+          <t>关键元素 /debug/xfer:刷新设备</t>
         </is>
       </c>
       <c r="D580" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/debug/xfer:\u5237\u65b0\u8bbe\u5907</t>
+          <t>关键元素可见：/debug/xfer:刷新设备</t>
         </is>
       </c>
       <c r="E580" s="2" t="n"/>
@@ -20163,7 +20213,7 @@
         </is>
       </c>
     </row>
-    <row r="581">
+    <row r="581" ht="42" customHeight="1">
       <c r="A581" s="2" t="n">
         <v>580</v>
       </c>
@@ -20174,12 +20224,12 @@
       </c>
       <c r="C581" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /debug/configFile:\u91cd\u65b0\u8f7d\u5165\u914d\u7f6e</t>
+          <t>关键元素 /debug/configFile:重新载入配置</t>
         </is>
       </c>
       <c r="D581" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/debug/configFile:\u91cd\u65b0\u8f7d\u5165\u914d\u7f6e</t>
+          <t>关键元素可见：/debug/configFile:重新载入配置</t>
         </is>
       </c>
       <c r="E581" s="2" t="n"/>
@@ -20197,7 +20247,7 @@
         </is>
       </c>
     </row>
-    <row r="582">
+    <row r="582" ht="28" customHeight="1">
       <c r="A582" s="2" t="n">
         <v>581</v>
       </c>
@@ -20208,12 +20258,12 @@
       </c>
       <c r="C582" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /debug/configFile:\u4e0a\u4f20</t>
+          <t>关键元素 /debug/configFile:上传</t>
         </is>
       </c>
       <c r="D582" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/debug/configFile:\u4e0a\u4f20</t>
+          <t>关键元素可见：/debug/configFile:上传</t>
         </is>
       </c>
       <c r="E582" s="2" t="n"/>
@@ -20231,7 +20281,7 @@
         </is>
       </c>
     </row>
-    <row r="583">
+    <row r="583" ht="28" customHeight="1">
       <c r="A583" s="2" t="n">
         <v>582</v>
       </c>
@@ -20242,12 +20292,12 @@
       </c>
       <c r="C583" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /debug/tmCalc:\u8ba1\u7b97</t>
+          <t>关键元素 /debug/tmCalc:计算</t>
         </is>
       </c>
       <c r="D583" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/debug/tmCalc:\u8ba1\u7b97</t>
+          <t>关键元素可见：/debug/tmCalc:计算</t>
         </is>
       </c>
       <c r="E583" s="2" t="n"/>
@@ -20265,7 +20315,7 @@
         </is>
       </c>
     </row>
-    <row r="584">
+    <row r="584" ht="28" customHeight="1">
       <c r="A584" s="2" t="n">
         <v>583</v>
       </c>
@@ -20276,12 +20326,12 @@
       </c>
       <c r="C584" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /debug/checksum:\u8ba1\u7b97</t>
+          <t>关键元素 /debug/checksum:计算</t>
         </is>
       </c>
       <c r="D584" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/debug/checksum:\u8ba1\u7b97</t>
+          <t>关键元素可见：/debug/checksum:计算</t>
         </is>
       </c>
       <c r="E584" s="2" t="n"/>
@@ -20299,7 +20349,7 @@
         </is>
       </c>
     </row>
-    <row r="585">
+    <row r="585" ht="28" customHeight="1">
       <c r="A585" s="2" t="n">
         <v>584</v>
       </c>
@@ -20310,12 +20360,12 @@
       </c>
       <c r="C585" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /debug/checksum:\u7b97\u6cd5\u9009\u62e9</t>
+          <t>关键元素 /debug/checksum:算法选择</t>
         </is>
       </c>
       <c r="D585" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/debug/checksum:\u7b97\u6cd5\u9009\u62e9</t>
+          <t>关键元素可见：/debug/checksum:算法选择</t>
         </is>
       </c>
       <c r="E585" s="2" t="n"/>
@@ -20333,7 +20383,7 @@
         </is>
       </c>
     </row>
-    <row r="586">
+    <row r="586" ht="28" customHeight="1">
       <c r="A586" s="2" t="n">
         <v>585</v>
       </c>
@@ -20344,12 +20394,12 @@
       </c>
       <c r="C586" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /debug/numconv:\u6570\u5b57\u8f6c HEX</t>
+          <t>关键元素 /debug/numconv:数字转 HEX</t>
         </is>
       </c>
       <c r="D586" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/debug/numconv:\u6570\u5b57\u8f6c HEX</t>
+          <t>关键元素可见：/debug/numconv:数字转 HEX</t>
         </is>
       </c>
       <c r="E586" s="2" t="n"/>
@@ -20367,7 +20417,7 @@
         </is>
       </c>
     </row>
-    <row r="587">
+    <row r="587" ht="28" customHeight="1">
       <c r="A587" s="2" t="n">
         <v>586</v>
       </c>
@@ -20378,12 +20428,12 @@
       </c>
       <c r="C587" s="2" t="inlineStr">
         <is>
-          <t>关键元素 /debug/numconv:\u8ba1\u7b97</t>
+          <t>关键元素 /debug/numconv:计算</t>
         </is>
       </c>
       <c r="D587" s="2" t="inlineStr">
         <is>
-          <t>关键元素可见：/debug/numconv:\u8ba1\u7b97</t>
+          <t>关键元素可见：/debug/numconv:计算</t>
         </is>
       </c>
       <c r="E587" s="2" t="n"/>
@@ -20401,7 +20451,7 @@
         </is>
       </c>
     </row>
-    <row r="588">
+    <row r="588" ht="28" customHeight="1">
       <c r="A588" s="2" t="n">
         <v>587</v>
       </c>
@@ -20435,7 +20485,7 @@
         </is>
       </c>
     </row>
-    <row r="589">
+    <row r="589" ht="28" customHeight="1">
       <c r="A589" s="2" t="n">
         <v>588</v>
       </c>
@@ -20469,7 +20519,7 @@
         </is>
       </c>
     </row>
-    <row r="590">
+    <row r="590" ht="28" customHeight="1">
       <c r="A590" s="2" t="n">
         <v>589</v>
       </c>
@@ -20503,7 +20553,7 @@
         </is>
       </c>
     </row>
-    <row r="591">
+    <row r="591" ht="28" customHeight="1">
       <c r="A591" s="2" t="n">
         <v>590</v>
       </c>
@@ -20537,7 +20587,7 @@
         </is>
       </c>
     </row>
-    <row r="592">
+    <row r="592" ht="28" customHeight="1">
       <c r="A592" s="2" t="n">
         <v>591</v>
       </c>
@@ -20571,7 +20621,7 @@
         </is>
       </c>
     </row>
-    <row r="593">
+    <row r="593" ht="28" customHeight="1">
       <c r="A593" s="2" t="n">
         <v>592</v>
       </c>
@@ -20605,7 +20655,7 @@
         </is>
       </c>
     </row>
-    <row r="594">
+    <row r="594" ht="28" customHeight="1">
       <c r="A594" s="2" t="n">
         <v>593</v>
       </c>
@@ -20639,7 +20689,7 @@
         </is>
       </c>
     </row>
-    <row r="595">
+    <row r="595" ht="28" customHeight="1">
       <c r="A595" s="2" t="n">
         <v>594</v>
       </c>
@@ -20673,7 +20723,7 @@
         </is>
       </c>
     </row>
-    <row r="596">
+    <row r="596" ht="28" customHeight="1">
       <c r="A596" s="2" t="n">
         <v>595</v>
       </c>
@@ -20707,7 +20757,7 @@
         </is>
       </c>
     </row>
-    <row r="597">
+    <row r="597" ht="28" customHeight="1">
       <c r="A597" s="2" t="n">
         <v>596</v>
       </c>
@@ -20741,7 +20791,7 @@
         </is>
       </c>
     </row>
-    <row r="598">
+    <row r="598" ht="28" customHeight="1">
       <c r="A598" s="2" t="n">
         <v>597</v>
       </c>
@@ -20775,7 +20825,7 @@
         </is>
       </c>
     </row>
-    <row r="599">
+    <row r="599" ht="28" customHeight="1">
       <c r="A599" s="2" t="n">
         <v>598</v>
       </c>
@@ -20809,7 +20859,7 @@
         </is>
       </c>
     </row>
-    <row r="600">
+    <row r="600" ht="28" customHeight="1">
       <c r="A600" s="2" t="n">
         <v>599</v>
       </c>
@@ -20843,7 +20893,7 @@
         </is>
       </c>
     </row>
-    <row r="601">
+    <row r="601" ht="28" customHeight="1">
       <c r="A601" s="2" t="n">
         <v>600</v>
       </c>
@@ -20877,7 +20927,7 @@
         </is>
       </c>
     </row>
-    <row r="602">
+    <row r="602" ht="28" customHeight="1">
       <c r="A602" s="2" t="n">
         <v>601</v>
       </c>
@@ -20911,7 +20961,7 @@
         </is>
       </c>
     </row>
-    <row r="603">
+    <row r="603" ht="28" customHeight="1">
       <c r="A603" s="2" t="n">
         <v>602</v>
       </c>
@@ -20945,7 +20995,7 @@
         </is>
       </c>
     </row>
-    <row r="604">
+    <row r="604" ht="28" customHeight="1">
       <c r="A604" s="2" t="n">
         <v>603</v>
       </c>
@@ -20979,7 +21029,7 @@
         </is>
       </c>
     </row>
-    <row r="605">
+    <row r="605" ht="28" customHeight="1">
       <c r="A605" s="2" t="n">
         <v>604</v>
       </c>
@@ -21013,7 +21063,7 @@
         </is>
       </c>
     </row>
-    <row r="606">
+    <row r="606" ht="28" customHeight="1">
       <c r="A606" s="2" t="n">
         <v>605</v>
       </c>
@@ -21047,7 +21097,7 @@
         </is>
       </c>
     </row>
-    <row r="607">
+    <row r="607" ht="28" customHeight="1">
       <c r="A607" s="2" t="n">
         <v>606</v>
       </c>
@@ -21081,7 +21131,7 @@
         </is>
       </c>
     </row>
-    <row r="608">
+    <row r="608" ht="28" customHeight="1">
       <c r="A608" s="2" t="n">
         <v>607</v>
       </c>
@@ -21115,7 +21165,7 @@
         </is>
       </c>
     </row>
-    <row r="609">
+    <row r="609" ht="28" customHeight="1">
       <c r="A609" s="2" t="n">
         <v>608</v>
       </c>
@@ -21149,7 +21199,7 @@
         </is>
       </c>
     </row>
-    <row r="610">
+    <row r="610" ht="28" customHeight="1">
       <c r="A610" s="2" t="n">
         <v>609</v>
       </c>
@@ -21183,7 +21233,7 @@
         </is>
       </c>
     </row>
-    <row r="611">
+    <row r="611" ht="28" customHeight="1">
       <c r="A611" s="2" t="n">
         <v>610</v>
       </c>
@@ -21217,7 +21267,7 @@
         </is>
       </c>
     </row>
-    <row r="612">
+    <row r="612" ht="28" customHeight="1">
       <c r="A612" s="2" t="n">
         <v>611</v>
       </c>
@@ -21251,7 +21301,7 @@
         </is>
       </c>
     </row>
-    <row r="613">
+    <row r="613" ht="28" customHeight="1">
       <c r="A613" s="2" t="n">
         <v>612</v>
       </c>
@@ -21285,7 +21335,7 @@
         </is>
       </c>
     </row>
-    <row r="614">
+    <row r="614" ht="42" customHeight="1">
       <c r="A614" s="2" t="n">
         <v>613</v>
       </c>
@@ -21319,7 +21369,7 @@
         </is>
       </c>
     </row>
-    <row r="615">
+    <row r="615" ht="42" customHeight="1">
       <c r="A615" s="2" t="n">
         <v>614</v>
       </c>
@@ -21353,7 +21403,7 @@
         </is>
       </c>
     </row>
-    <row r="616">
+    <row r="616" ht="42" customHeight="1">
       <c r="A616" s="2" t="n">
         <v>615</v>
       </c>
@@ -21387,7 +21437,7 @@
         </is>
       </c>
     </row>
-    <row r="617">
+    <row r="617" ht="28" customHeight="1">
       <c r="A617" s="2" t="n">
         <v>616</v>
       </c>
@@ -21421,7 +21471,7 @@
         </is>
       </c>
     </row>
-    <row r="618">
+    <row r="618" ht="28" customHeight="1">
       <c r="A618" s="2" t="n">
         <v>617</v>
       </c>
@@ -21455,7 +21505,7 @@
         </is>
       </c>
     </row>
-    <row r="619">
+    <row r="619" ht="28" customHeight="1">
       <c r="A619" s="2" t="n">
         <v>618</v>
       </c>
@@ -21489,7 +21539,7 @@
         </is>
       </c>
     </row>
-    <row r="620">
+    <row r="620" ht="28" customHeight="1">
       <c r="A620" s="2" t="n">
         <v>619</v>
       </c>
@@ -21523,7 +21573,7 @@
         </is>
       </c>
     </row>
-    <row r="621">
+    <row r="621" ht="28" customHeight="1">
       <c r="A621" s="2" t="n">
         <v>620</v>
       </c>
@@ -21557,7 +21607,7 @@
         </is>
       </c>
     </row>
-    <row r="622">
+    <row r="622" ht="28" customHeight="1">
       <c r="A622" s="2" t="n">
         <v>621</v>
       </c>
@@ -21591,7 +21641,7 @@
         </is>
       </c>
     </row>
-    <row r="623">
+    <row r="623" ht="28" customHeight="1">
       <c r="A623" s="2" t="n">
         <v>622</v>
       </c>
@@ -21625,7 +21675,7 @@
         </is>
       </c>
     </row>
-    <row r="624">
+    <row r="624" ht="28" customHeight="1">
       <c r="A624" s="2" t="n">
         <v>623</v>
       </c>
@@ -21659,7 +21709,7 @@
         </is>
       </c>
     </row>
-    <row r="625">
+    <row r="625" ht="28" customHeight="1">
       <c r="A625" s="2" t="n">
         <v>624</v>
       </c>
@@ -21693,7 +21743,7 @@
         </is>
       </c>
     </row>
-    <row r="626">
+    <row r="626" ht="28" customHeight="1">
       <c r="A626" s="2" t="n">
         <v>625</v>
       </c>
@@ -21727,7 +21777,7 @@
         </is>
       </c>
     </row>
-    <row r="627">
+    <row r="627" ht="28" customHeight="1">
       <c r="A627" s="2" t="n">
         <v>626</v>
       </c>
@@ -21761,7 +21811,7 @@
         </is>
       </c>
     </row>
-    <row r="628">
+    <row r="628" ht="28" customHeight="1">
       <c r="A628" s="2" t="n">
         <v>627</v>
       </c>
@@ -21795,7 +21845,7 @@
         </is>
       </c>
     </row>
-    <row r="629">
+    <row r="629" ht="28" customHeight="1">
       <c r="A629" s="2" t="n">
         <v>628</v>
       </c>
@@ -21829,7 +21879,7 @@
         </is>
       </c>
     </row>
-    <row r="630">
+    <row r="630" ht="28" customHeight="1">
       <c r="A630" s="2" t="n">
         <v>629</v>
       </c>
@@ -21863,7 +21913,7 @@
         </is>
       </c>
     </row>
-    <row r="631">
+    <row r="631" ht="28" customHeight="1">
       <c r="A631" s="2" t="n">
         <v>630</v>
       </c>
@@ -21897,7 +21947,7 @@
         </is>
       </c>
     </row>
-    <row r="632">
+    <row r="632" ht="28" customHeight="1">
       <c r="A632" s="2" t="n">
         <v>631</v>
       </c>
@@ -21931,7 +21981,7 @@
         </is>
       </c>
     </row>
-    <row r="633">
+    <row r="633" ht="28" customHeight="1">
       <c r="A633" s="2" t="n">
         <v>632</v>
       </c>
@@ -21965,7 +22015,7 @@
         </is>
       </c>
     </row>
-    <row r="634">
+    <row r="634" ht="28" customHeight="1">
       <c r="A634" s="2" t="n">
         <v>633</v>
       </c>
@@ -21999,7 +22049,7 @@
         </is>
       </c>
     </row>
-    <row r="635">
+    <row r="635" ht="28" customHeight="1">
       <c r="A635" s="2" t="n">
         <v>634</v>
       </c>
@@ -22033,7 +22083,7 @@
         </is>
       </c>
     </row>
-    <row r="636">
+    <row r="636" ht="28" customHeight="1">
       <c r="A636" s="2" t="n">
         <v>635</v>
       </c>
@@ -22067,7 +22117,7 @@
         </is>
       </c>
     </row>
-    <row r="637">
+    <row r="637" ht="28" customHeight="1">
       <c r="A637" s="2" t="n">
         <v>636</v>
       </c>
@@ -22101,7 +22151,7 @@
         </is>
       </c>
     </row>
-    <row r="638">
+    <row r="638" ht="28" customHeight="1">
       <c r="A638" s="2" t="n">
         <v>637</v>
       </c>
@@ -22135,7 +22185,7 @@
         </is>
       </c>
     </row>
-    <row r="639">
+    <row r="639" ht="28" customHeight="1">
       <c r="A639" s="2" t="n">
         <v>638</v>
       </c>
@@ -22169,7 +22219,7 @@
         </is>
       </c>
     </row>
-    <row r="640">
+    <row r="640" ht="28" customHeight="1">
       <c r="A640" s="2" t="n">
         <v>639</v>
       </c>
@@ -22203,7 +22253,7 @@
         </is>
       </c>
     </row>
-    <row r="641">
+    <row r="641" ht="28" customHeight="1">
       <c r="A641" s="2" t="n">
         <v>640</v>
       </c>
@@ -22237,7 +22287,7 @@
         </is>
       </c>
     </row>
-    <row r="642">
+    <row r="642" ht="28" customHeight="1">
       <c r="A642" s="2" t="n">
         <v>641</v>
       </c>
@@ -22271,7 +22321,7 @@
         </is>
       </c>
     </row>
-    <row r="643">
+    <row r="643" ht="28" customHeight="1">
       <c r="A643" s="2" t="n">
         <v>642</v>
       </c>
@@ -22305,7 +22355,7 @@
         </is>
       </c>
     </row>
-    <row r="644">
+    <row r="644" ht="28" customHeight="1">
       <c r="A644" s="2" t="n">
         <v>643</v>
       </c>
@@ -22339,7 +22389,7 @@
         </is>
       </c>
     </row>
-    <row r="645">
+    <row r="645" ht="28" customHeight="1">
       <c r="A645" s="2" t="n">
         <v>644</v>
       </c>
@@ -22373,7 +22423,7 @@
         </is>
       </c>
     </row>
-    <row r="646">
+    <row r="646" ht="28" customHeight="1">
       <c r="A646" s="2" t="n">
         <v>645</v>
       </c>
@@ -22407,7 +22457,7 @@
         </is>
       </c>
     </row>
-    <row r="647">
+    <row r="647" ht="28" customHeight="1">
       <c r="A647" s="2" t="n">
         <v>646</v>
       </c>
@@ -22441,7 +22491,7 @@
         </is>
       </c>
     </row>
-    <row r="648">
+    <row r="648" ht="28" customHeight="1">
       <c r="A648" s="2" t="n">
         <v>647</v>
       </c>
@@ -22475,7 +22525,7 @@
         </is>
       </c>
     </row>
-    <row r="649">
+    <row r="649" ht="28" customHeight="1">
       <c r="A649" s="2" t="n">
         <v>648</v>
       </c>
@@ -22509,7 +22559,7 @@
         </is>
       </c>
     </row>
-    <row r="650">
+    <row r="650" ht="28" customHeight="1">
       <c r="A650" s="2" t="n">
         <v>649</v>
       </c>
@@ -22543,7 +22593,7 @@
         </is>
       </c>
     </row>
-    <row r="651">
+    <row r="651" ht="28" customHeight="1">
       <c r="A651" s="2" t="n">
         <v>650</v>
       </c>
@@ -22577,7 +22627,7 @@
         </is>
       </c>
     </row>
-    <row r="652">
+    <row r="652" ht="28" customHeight="1">
       <c r="A652" s="2" t="n">
         <v>651</v>
       </c>
@@ -22607,7 +22657,7 @@
         </is>
       </c>
     </row>
-    <row r="653">
+    <row r="653" ht="28" customHeight="1">
       <c r="A653" s="2" t="n">
         <v>652</v>
       </c>
@@ -22637,7 +22687,7 @@
         </is>
       </c>
     </row>
-    <row r="654">
+    <row r="654" ht="28" customHeight="1">
       <c r="A654" s="2" t="n">
         <v>653</v>
       </c>
@@ -22667,7 +22717,7 @@
         </is>
       </c>
     </row>
-    <row r="655">
+    <row r="655" ht="28" customHeight="1">
       <c r="A655" s="2" t="n">
         <v>654</v>
       </c>
@@ -22697,7 +22747,7 @@
         </is>
       </c>
     </row>
-    <row r="656">
+    <row r="656" ht="28" customHeight="1">
       <c r="A656" s="2" t="n">
         <v>655</v>
       </c>
@@ -22727,7 +22777,7 @@
         </is>
       </c>
     </row>
-    <row r="657">
+    <row r="657" ht="18" customHeight="1">
       <c r="A657" s="2" t="n">
         <v>656</v>
       </c>
@@ -22757,7 +22807,7 @@
         </is>
       </c>
     </row>
-    <row r="658">
+    <row r="658" ht="18" customHeight="1">
       <c r="A658" s="2" t="n">
         <v>657</v>
       </c>
@@ -22787,7 +22837,7 @@
         </is>
       </c>
     </row>
-    <row r="659">
+    <row r="659" ht="18" customHeight="1">
       <c r="A659" s="2" t="n">
         <v>658</v>
       </c>
@@ -22817,7 +22867,7 @@
         </is>
       </c>
     </row>
-    <row r="660">
+    <row r="660" ht="18" customHeight="1">
       <c r="A660" s="2" t="n">
         <v>659</v>
       </c>
@@ -22847,7 +22897,7 @@
         </is>
       </c>
     </row>
-    <row r="661">
+    <row r="661" ht="18" customHeight="1">
       <c r="A661" s="2" t="n">
         <v>660</v>
       </c>
@@ -22877,7 +22927,7 @@
         </is>
       </c>
     </row>
-    <row r="662">
+    <row r="662" ht="28" customHeight="1">
       <c r="A662" s="2" t="n">
         <v>661</v>
       </c>
@@ -22907,7 +22957,7 @@
         </is>
       </c>
     </row>
-    <row r="663">
+    <row r="663" ht="18" customHeight="1">
       <c r="A663" s="2" t="n">
         <v>662</v>
       </c>
@@ -22937,7 +22987,7 @@
         </is>
       </c>
     </row>
-    <row r="664">
+    <row r="664" ht="18" customHeight="1">
       <c r="A664" s="2" t="n">
         <v>663</v>
       </c>
@@ -22967,7 +23017,7 @@
         </is>
       </c>
     </row>
-    <row r="665">
+    <row r="665" ht="28" customHeight="1">
       <c r="A665" s="2" t="n">
         <v>664</v>
       </c>
@@ -22997,7 +23047,7 @@
         </is>
       </c>
     </row>
-    <row r="666">
+    <row r="666" ht="18" customHeight="1">
       <c r="A666" s="2" t="n">
         <v>665</v>
       </c>
@@ -23027,7 +23077,7 @@
         </is>
       </c>
     </row>
-    <row r="667">
+    <row r="667" ht="18" customHeight="1">
       <c r="A667" s="2" t="n">
         <v>666</v>
       </c>
@@ -23057,7 +23107,7 @@
         </is>
       </c>
     </row>
-    <row r="668">
+    <row r="668" ht="18" customHeight="1">
       <c r="A668" s="2" t="n">
         <v>667</v>
       </c>
@@ -23087,7 +23137,7 @@
         </is>
       </c>
     </row>
-    <row r="669">
+    <row r="669" ht="28" customHeight="1">
       <c r="A669" s="2" t="n">
         <v>668</v>
       </c>
@@ -23117,7 +23167,7 @@
         </is>
       </c>
     </row>
-    <row r="670">
+    <row r="670" ht="28" customHeight="1">
       <c r="A670" s="2" t="n">
         <v>669</v>
       </c>
@@ -23147,7 +23197,7 @@
         </is>
       </c>
     </row>
-    <row r="671">
+    <row r="671" ht="18" customHeight="1">
       <c r="A671" s="2" t="n">
         <v>670</v>
       </c>
@@ -23177,7 +23227,7 @@
         </is>
       </c>
     </row>
-    <row r="672">
+    <row r="672" ht="28" customHeight="1">
       <c r="A672" s="2" t="n">
         <v>671</v>
       </c>
@@ -23207,7 +23257,7 @@
         </is>
       </c>
     </row>
-    <row r="673">
+    <row r="673" ht="28" customHeight="1">
       <c r="A673" s="2" t="n">
         <v>672</v>
       </c>
@@ -23237,7 +23287,7 @@
         </is>
       </c>
     </row>
-    <row r="674">
+    <row r="674" ht="28" customHeight="1">
       <c r="A674" s="2" t="n">
         <v>673</v>
       </c>
@@ -23267,7 +23317,7 @@
         </is>
       </c>
     </row>
-    <row r="675">
+    <row r="675" ht="28" customHeight="1">
       <c r="A675" s="2" t="n">
         <v>674</v>
       </c>
@@ -23298,6 +23348,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J675"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23310,206 +23361,214 @@
   </sheetPr>
   <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>模块</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>用例数</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>建议测试人</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>完成数</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>通过数</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>HIL·CAN</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>HIL·CAN</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n">
         <v>275</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>HIL·串口</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="4" t="n">
         <v>113</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>UI冒烟</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="4" t="n">
         <v>95</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>调试·深测</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="4" t="n">
         <v>65</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>自检·单元</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="4" t="n">
         <v>57</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>HIL·UDP</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="4" t="n">
         <v>33</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>调试·数据模拟</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="4" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>遥测</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="4" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>数据库·结构</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="4" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>调试</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="4" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>单板</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>遥控-BIU</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>遥控-XL</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>遥控-YJ216</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>单板·YJ216</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="4" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>首页</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="4" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" s="4" t="n">
         <v>674</v>
       </c>
     </row>
@@ -23526,16 +23585,19 @@
   </sheetPr>
   <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="100" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>由 python -m hil.report sync 重建：以 pytest 实采自动化 + 现网业务页（排除若依 system/monitor/tool）为准；旧清单不作权威。自动化ID=pytest nodeid；空=页面功能待补自动化。填报：python -m hil.report fill &lt;run_dir&gt;。禁止生成 .bak。</t>
         </is>
